--- a/202660_UAX_OfertaLenguas.xlsx
+++ b/202660_UAX_OfertaLenguas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202660/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{2F2356BF-5FED-4956-B6D5-A4DB07EC43D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48E02413-7EE3-4DA5-9333-60B79D1CAE52}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{2F2356BF-5FED-4956-B6D5-A4DB07EC43D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D697DB6-0142-44D4-8FA0-2382541B75C0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="227">
   <si>
     <t>NRC</t>
   </si>
@@ -294,18 +294,9 @@
     <t>XLEN101</t>
   </si>
   <si>
-    <t>XLEN102</t>
-  </si>
-  <si>
-    <t>XLEN103</t>
-  </si>
-  <si>
     <t>Recordatorio</t>
   </si>
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
     <t>Inglés requisito</t>
   </si>
   <si>
@@ -426,15 +417,9 @@
     <t>1,3,5</t>
   </si>
   <si>
-    <t>⚠️ Atención: Este curso debe inscribirse obligatoriamente junto con el NRC 40693.</t>
-  </si>
-  <si>
     <t>TIDI0303</t>
   </si>
   <si>
-    <t>⚠️ Atención: Este curso debe inscribirse obligatoriamente junto con el NRC 40694.</t>
-  </si>
-  <si>
     <t>TCUG0432</t>
   </si>
   <si>
@@ -444,39 +429,15 @@
     <t>2,4</t>
   </si>
   <si>
-    <t>⚠️ Atención: Este curso debe inscribirse obligatoriamente junto con el NRC 40691.</t>
-  </si>
-  <si>
     <t>TIDI0302</t>
   </si>
   <si>
     <t>English grammar</t>
   </si>
   <si>
-    <t>⚠️ Atención: Este curso debe inscribirse obligatoriamente junto con el NRC 40692.</t>
-  </si>
-  <si>
     <t>García Pérez Alfredo</t>
   </si>
   <si>
-    <t>XLEN104</t>
-  </si>
-  <si>
-    <t>⚠️ Atención: Este curso debe inscribirse obligatoriamente junto con el NRC 40696.</t>
-  </si>
-  <si>
-    <t>XLEN105</t>
-  </si>
-  <si>
-    <t>⚠️ Atención: Este curso debe inscribirse obligatoriamente junto con el NRC 40695.</t>
-  </si>
-  <si>
-    <t>⚠️ Atención: Este curso debe inscribirse obligatoriamente junto con el NRC 40698.</t>
-  </si>
-  <si>
-    <t>⚠️ Atención: Este curso debe inscribirse obligatoriamente junto con el NRC 40697.</t>
-  </si>
-  <si>
     <t>XLEN106</t>
   </si>
   <si>
@@ -748,6 +709,30 @@
   </si>
   <si>
     <t>5°nivel de italiano</t>
+  </si>
+  <si>
+    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40693.</t>
+  </si>
+  <si>
+    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40694.</t>
+  </si>
+  <si>
+    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40691.</t>
+  </si>
+  <si>
+    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40692.</t>
+  </si>
+  <si>
+    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40696.</t>
+  </si>
+  <si>
+    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40695.</t>
+  </si>
+  <si>
+    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40698.</t>
+  </si>
+  <si>
+    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40697.</t>
   </si>
 </sst>
 </file>
@@ -1291,7 +1276,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1306,9 +1291,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2236,6 +2218,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Método_de_instrucción" xr10:uid="{03F1D03D-BB1E-40EA-87DF-1313DFC6A3BE}" sourceName="MetodoInstruccion">
   <extLst>
@@ -2286,8 +2272,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:O163" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A1:O163" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O2">
-    <sortCondition ref="G1:G2"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O163">
+    <sortCondition ref="B1:B163"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="ClaveBanner" dataDxfId="14"/>
@@ -2690,8 +2676,8 @@
       <c r="N1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="8" t="s">
-        <v>82</v>
+      <c r="O1" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2702,7 +2688,7 @@
         <v>40493</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
         <v>40</v>
@@ -2714,16 +2700,16 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J2" t="s">
         <v>85</v>
-      </c>
-      <c r="H2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J2" t="s">
-        <v>88</v>
       </c>
       <c r="K2" t="s">
         <v>73</v>
@@ -2743,7 +2729,7 @@
         <v>40494</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
         <v>57</v>
@@ -2755,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K3" t="s">
         <v>73</v>
@@ -2784,7 +2770,7 @@
         <v>40495</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
         <v>40</v>
@@ -2796,16 +2782,16 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" t="s">
         <v>85</v>
-      </c>
-      <c r="H4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" t="s">
-        <v>88</v>
       </c>
       <c r="K4" t="s">
         <v>73</v>
@@ -2825,7 +2811,7 @@
         <v>40496</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
@@ -2837,16 +2823,16 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K5" t="s">
         <v>73</v>
@@ -2866,7 +2852,7 @@
         <v>40501</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
         <v>40</v>
@@ -2878,16 +2864,16 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K6" t="s">
         <v>73</v>
@@ -2907,7 +2893,7 @@
         <v>40502</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -2919,16 +2905,16 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" t="s">
         <v>89</v>
-      </c>
-      <c r="H7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" t="s">
-        <v>91</v>
-      </c>
-      <c r="J7" t="s">
-        <v>92</v>
       </c>
       <c r="K7" t="s">
         <v>73</v>
@@ -2948,7 +2934,7 @@
         <v>40503</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
@@ -2960,16 +2946,16 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K8" t="s">
         <v>73</v>
@@ -2989,7 +2975,7 @@
         <v>40504</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -3001,16 +2987,16 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" t="s">
         <v>89</v>
-      </c>
-      <c r="H9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" t="s">
-        <v>91</v>
-      </c>
-      <c r="J9" t="s">
-        <v>92</v>
       </c>
       <c r="K9" t="s">
         <v>73</v>
@@ -3030,7 +3016,7 @@
         <v>40505</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
         <v>40</v>
@@ -3042,16 +3028,16 @@
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K10" t="s">
         <v>73</v>
@@ -3071,7 +3057,7 @@
         <v>40506</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
         <v>57</v>
@@ -3083,16 +3069,16 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11" t="s">
         <v>89</v>
-      </c>
-      <c r="H11" t="s">
-        <v>93</v>
-      </c>
-      <c r="I11" t="s">
-        <v>91</v>
-      </c>
-      <c r="J11" t="s">
-        <v>92</v>
       </c>
       <c r="K11" t="s">
         <v>73</v>
@@ -3112,7 +3098,7 @@
         <v>40513</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
         <v>40</v>
@@ -3124,16 +3110,16 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s">
         <v>73</v>
@@ -3153,7 +3139,7 @@
         <v>40514</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
@@ -3165,16 +3151,16 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s">
         <v>73</v>
@@ -3194,7 +3180,7 @@
         <v>40517</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>40</v>
@@ -3206,16 +3192,16 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s">
         <v>67</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s">
         <v>73</v>
@@ -3235,7 +3221,7 @@
         <v>40518</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
         <v>57</v>
@@ -3247,16 +3233,16 @@
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s">
         <v>67</v>
       </c>
       <c r="I15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J15" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s">
         <v>73</v>
@@ -3276,7 +3262,7 @@
         <v>40525</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
         <v>43</v>
@@ -3288,16 +3274,16 @@
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K16" t="s">
         <v>73</v>
@@ -3317,7 +3303,7 @@
         <v>40526</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
         <v>63</v>
@@ -3329,16 +3315,16 @@
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K17" t="s">
         <v>73</v>
@@ -3358,7 +3344,7 @@
         <v>40527</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
         <v>43</v>
@@ -3370,16 +3356,16 @@
         <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s">
         <v>64</v>
       </c>
       <c r="I18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K18" t="s">
         <v>73</v>
@@ -3399,7 +3385,7 @@
         <v>40528</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
         <v>63</v>
@@ -3411,16 +3397,16 @@
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s">
         <v>64</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K19" t="s">
         <v>73</v>
@@ -3440,7 +3426,7 @@
         <v>40529</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>43</v>
@@ -3452,16 +3438,16 @@
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
         <v>44</v>
       </c>
       <c r="I20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K20" t="s">
         <v>73</v>
@@ -3481,7 +3467,7 @@
         <v>40530</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
         <v>63</v>
@@ -3493,16 +3479,16 @@
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
         <v>44</v>
       </c>
       <c r="I21" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K21" t="s">
         <v>73</v>
@@ -3522,7 +3508,7 @@
         <v>40531</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
         <v>43</v>
@@ -3534,16 +3520,16 @@
         <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s">
         <v>61</v>
       </c>
       <c r="I22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s">
         <v>73</v>
@@ -3563,7 +3549,7 @@
         <v>40532</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
         <v>63</v>
@@ -3575,16 +3561,16 @@
         <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
         <v>61</v>
       </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s">
         <v>73</v>
@@ -3604,7 +3590,7 @@
         <v>40539</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -3616,16 +3602,16 @@
         <v>9</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s">
         <v>41</v>
       </c>
       <c r="I24" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s">
         <v>73</v>
@@ -3645,7 +3631,7 @@
         <v>40540</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
         <v>63</v>
@@ -3657,16 +3643,16 @@
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s">
         <v>41</v>
       </c>
       <c r="I25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s">
         <v>73</v>
@@ -3686,7 +3672,7 @@
         <v>40541</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
         <v>43</v>
@@ -3698,16 +3684,16 @@
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I26" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s">
         <v>73</v>
@@ -3727,7 +3713,7 @@
         <v>40542</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
         <v>63</v>
@@ -3739,16 +3725,16 @@
         <v>9</v>
       </c>
       <c r="G27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J27" t="s">
         <v>89</v>
-      </c>
-      <c r="H27" t="s">
-        <v>101</v>
-      </c>
-      <c r="I27" t="s">
-        <v>91</v>
-      </c>
-      <c r="J27" t="s">
-        <v>92</v>
       </c>
       <c r="K27" t="s">
         <v>73</v>
@@ -3768,7 +3754,7 @@
         <v>40543</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
         <v>43</v>
@@ -3780,16 +3766,16 @@
         <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s">
         <v>47</v>
       </c>
       <c r="I28" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J28" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s">
         <v>73</v>
@@ -3809,7 +3795,7 @@
         <v>40544</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
         <v>63</v>
@@ -3821,16 +3807,16 @@
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s">
         <v>47</v>
       </c>
       <c r="I29" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s">
         <v>73</v>
@@ -3850,7 +3836,7 @@
         <v>40551</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
         <v>43</v>
@@ -3862,16 +3848,16 @@
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I30" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J30" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K30" t="s">
         <v>73</v>
@@ -3891,7 +3877,7 @@
         <v>40552</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
         <v>63</v>
@@ -3903,16 +3889,16 @@
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I31" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J31" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s">
         <v>73</v>
@@ -3932,7 +3918,7 @@
         <v>40555</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
         <v>43</v>
@@ -3944,16 +3930,16 @@
         <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s">
         <v>47</v>
       </c>
       <c r="I32" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J32" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s">
         <v>73</v>
@@ -3973,7 +3959,7 @@
         <v>40556</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
         <v>63</v>
@@ -3985,16 +3971,16 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s">
         <v>47</v>
       </c>
       <c r="I33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J33" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s">
         <v>73</v>
@@ -4014,7 +4000,7 @@
         <v>40563</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
         <v>46</v>
@@ -4026,16 +4012,16 @@
         <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J34" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K34" t="s">
         <v>73</v>
@@ -4055,7 +4041,7 @@
         <v>40564</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D35" t="s">
         <v>49</v>
@@ -4067,16 +4053,16 @@
         <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I35" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J35" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K35" t="s">
         <v>73</v>
@@ -4096,7 +4082,7 @@
         <v>40565</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
@@ -4108,16 +4094,16 @@
         <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s">
         <v>41</v>
       </c>
       <c r="I36" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J36" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s">
         <v>73</v>
@@ -4137,7 +4123,7 @@
         <v>40566</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
         <v>49</v>
@@ -4149,16 +4135,16 @@
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s">
         <v>41</v>
       </c>
       <c r="I37" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J37" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s">
         <v>73</v>
@@ -4178,7 +4164,7 @@
         <v>40567</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
@@ -4190,16 +4176,16 @@
         <v>9</v>
       </c>
       <c r="G38" t="s">
+        <v>82</v>
+      </c>
+      <c r="H38" t="s">
+        <v>101</v>
+      </c>
+      <c r="I38" t="s">
+        <v>84</v>
+      </c>
+      <c r="J38" t="s">
         <v>85</v>
-      </c>
-      <c r="H38" t="s">
-        <v>104</v>
-      </c>
-      <c r="I38" t="s">
-        <v>87</v>
-      </c>
-      <c r="J38" t="s">
-        <v>88</v>
       </c>
       <c r="K38" t="s">
         <v>73</v>
@@ -4219,7 +4205,7 @@
         <v>40568</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
         <v>49</v>
@@ -4231,16 +4217,16 @@
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I39" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J39" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s">
         <v>73</v>
@@ -4260,7 +4246,7 @@
         <v>40569</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D40" t="s">
         <v>46</v>
@@ -4272,16 +4258,16 @@
         <v>9</v>
       </c>
       <c r="G40" t="s">
+        <v>82</v>
+      </c>
+      <c r="H40" t="s">
+        <v>98</v>
+      </c>
+      <c r="I40" t="s">
+        <v>84</v>
+      </c>
+      <c r="J40" t="s">
         <v>85</v>
-      </c>
-      <c r="H40" t="s">
-        <v>101</v>
-      </c>
-      <c r="I40" t="s">
-        <v>87</v>
-      </c>
-      <c r="J40" t="s">
-        <v>88</v>
       </c>
       <c r="K40" t="s">
         <v>73</v>
@@ -4301,7 +4287,7 @@
         <v>40570</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D41" t="s">
         <v>49</v>
@@ -4313,16 +4299,16 @@
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I41" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s">
         <v>73</v>
@@ -4342,7 +4328,7 @@
         <v>40571</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D42" t="s">
         <v>46</v>
@@ -4354,16 +4340,16 @@
         <v>9</v>
       </c>
       <c r="G42" t="s">
+        <v>82</v>
+      </c>
+      <c r="H42" t="s">
+        <v>102</v>
+      </c>
+      <c r="I42" t="s">
+        <v>84</v>
+      </c>
+      <c r="J42" t="s">
         <v>85</v>
-      </c>
-      <c r="H42" t="s">
-        <v>105</v>
-      </c>
-      <c r="I42" t="s">
-        <v>87</v>
-      </c>
-      <c r="J42" t="s">
-        <v>88</v>
       </c>
       <c r="K42" t="s">
         <v>73</v>
@@ -4383,7 +4369,7 @@
         <v>40572</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
         <v>49</v>
@@ -4395,16 +4381,16 @@
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I43" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J43" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K43" t="s">
         <v>73</v>
@@ -4424,7 +4410,7 @@
         <v>40573</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D44" t="s">
         <v>46</v>
@@ -4436,16 +4422,16 @@
         <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s">
         <v>66</v>
       </c>
       <c r="I44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J44" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K44" t="s">
         <v>73</v>
@@ -4465,7 +4451,7 @@
         <v>40574</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D45" t="s">
         <v>49</v>
@@ -4477,16 +4463,16 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s">
         <v>66</v>
       </c>
       <c r="I45" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J45" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K45" t="s">
         <v>73</v>
@@ -4506,7 +4492,7 @@
         <v>40585</v>
       </c>
       <c r="C46" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D46" t="s">
         <v>46</v>
@@ -4518,16 +4504,16 @@
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s">
         <v>64</v>
       </c>
       <c r="I46" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J46" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s">
         <v>73</v>
@@ -4547,7 +4533,7 @@
         <v>40586</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
         <v>49</v>
@@ -4559,16 +4545,16 @@
         <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s">
         <v>64</v>
       </c>
       <c r="I47" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J47" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s">
         <v>73</v>
@@ -4588,7 +4574,7 @@
         <v>40587</v>
       </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
         <v>46</v>
@@ -4600,16 +4586,16 @@
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I48" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J48" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s">
         <v>73</v>
@@ -4629,7 +4615,7 @@
         <v>40588</v>
       </c>
       <c r="C49" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D49" t="s">
         <v>49</v>
@@ -4641,16 +4627,16 @@
         <v>9</v>
       </c>
       <c r="G49" t="s">
+        <v>86</v>
+      </c>
+      <c r="H49" t="s">
+        <v>103</v>
+      </c>
+      <c r="I49" t="s">
+        <v>88</v>
+      </c>
+      <c r="J49" t="s">
         <v>89</v>
-      </c>
-      <c r="H49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I49" t="s">
-        <v>91</v>
-      </c>
-      <c r="J49" t="s">
-        <v>92</v>
       </c>
       <c r="K49" t="s">
         <v>73</v>
@@ -4670,7 +4656,7 @@
         <v>40589</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D50" t="s">
         <v>46</v>
@@ -4682,16 +4668,16 @@
         <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s">
         <v>44</v>
       </c>
       <c r="I50" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J50" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s">
         <v>73</v>
@@ -4711,7 +4697,7 @@
         <v>40590</v>
       </c>
       <c r="C51" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D51" t="s">
         <v>49</v>
@@ -4723,16 +4709,16 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H51" t="s">
         <v>44</v>
       </c>
       <c r="I51" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J51" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s">
         <v>73</v>
@@ -4752,7 +4738,7 @@
         <v>40591</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D52" t="s">
         <v>46</v>
@@ -4764,16 +4750,16 @@
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s">
         <v>66</v>
       </c>
       <c r="I52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J52" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s">
         <v>73</v>
@@ -4793,7 +4779,7 @@
         <v>40592</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D53" t="s">
         <v>49</v>
@@ -4805,16 +4791,16 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s">
         <v>66</v>
       </c>
       <c r="I53" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J53" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s">
         <v>73</v>
@@ -4834,7 +4820,7 @@
         <v>40593</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D54" t="s">
         <v>46</v>
@@ -4846,16 +4832,16 @@
         <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I54" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J54" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K54" t="s">
         <v>73</v>
@@ -4875,7 +4861,7 @@
         <v>40594</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D55" t="s">
         <v>49</v>
@@ -4887,16 +4873,16 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
+        <v>86</v>
+      </c>
+      <c r="H55" t="s">
+        <v>102</v>
+      </c>
+      <c r="I55" t="s">
+        <v>88</v>
+      </c>
+      <c r="J55" t="s">
         <v>89</v>
-      </c>
-      <c r="H55" t="s">
-        <v>105</v>
-      </c>
-      <c r="I55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J55" t="s">
-        <v>92</v>
       </c>
       <c r="K55" t="s">
         <v>73</v>
@@ -4916,7 +4902,7 @@
         <v>40595</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D56" t="s">
         <v>46</v>
@@ -4928,16 +4914,16 @@
         <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s">
         <v>61</v>
       </c>
       <c r="I56" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J56" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K56" t="s">
         <v>73</v>
@@ -4957,7 +4943,7 @@
         <v>40596</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D57" t="s">
         <v>49</v>
@@ -4969,16 +4955,16 @@
         <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s">
         <v>61</v>
       </c>
       <c r="I57" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J57" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s">
         <v>73</v>
@@ -4998,7 +4984,7 @@
         <v>40611</v>
       </c>
       <c r="C58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
         <v>46</v>
@@ -5010,16 +4996,16 @@
         <v>9</v>
       </c>
       <c r="G58" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s">
         <v>66</v>
       </c>
       <c r="I58" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J58" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s">
         <v>73</v>
@@ -5039,7 +5025,7 @@
         <v>40612</v>
       </c>
       <c r="C59" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D59" t="s">
         <v>49</v>
@@ -5051,16 +5037,16 @@
         <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H59" t="s">
         <v>66</v>
       </c>
       <c r="I59" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J59" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s">
         <v>73</v>
@@ -5080,7 +5066,7 @@
         <v>40619</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D60" t="s">
         <v>55</v>
@@ -5092,16 +5078,16 @@
         <v>9</v>
       </c>
       <c r="G60" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I60" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J60" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K60" t="s">
         <v>73</v>
@@ -5121,7 +5107,7 @@
         <v>40620</v>
       </c>
       <c r="C61" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D61" t="s">
         <v>51</v>
@@ -5133,16 +5119,16 @@
         <v>9</v>
       </c>
       <c r="G61" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H61" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I61" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J61" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K61" t="s">
         <v>73</v>
@@ -5162,7 +5148,7 @@
         <v>40621</v>
       </c>
       <c r="C62" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D62" t="s">
         <v>55</v>
@@ -5174,16 +5160,16 @@
         <v>9</v>
       </c>
       <c r="G62" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s">
         <v>53</v>
       </c>
       <c r="I62" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J62" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K62" t="s">
         <v>73</v>
@@ -5203,7 +5189,7 @@
         <v>40622</v>
       </c>
       <c r="C63" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D63" t="s">
         <v>51</v>
@@ -5215,16 +5201,16 @@
         <v>9</v>
       </c>
       <c r="G63" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H63" t="s">
         <v>53</v>
       </c>
       <c r="I63" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J63" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K63" t="s">
         <v>73</v>
@@ -5244,7 +5230,7 @@
         <v>40623</v>
       </c>
       <c r="C64" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D64" t="s">
         <v>55</v>
@@ -5256,16 +5242,16 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s">
         <v>65</v>
       </c>
       <c r="I64" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J64" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K64" t="s">
         <v>73</v>
@@ -5285,7 +5271,7 @@
         <v>40624</v>
       </c>
       <c r="C65" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D65" t="s">
         <v>51</v>
@@ -5297,16 +5283,16 @@
         <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H65" t="s">
         <v>65</v>
       </c>
       <c r="I65" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J65" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s">
         <v>73</v>
@@ -5326,7 +5312,7 @@
         <v>40625</v>
       </c>
       <c r="C66" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D66" t="s">
         <v>55</v>
@@ -5338,16 +5324,16 @@
         <v>9</v>
       </c>
       <c r="G66" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s">
         <v>58</v>
       </c>
       <c r="I66" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J66" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K66" t="s">
         <v>73</v>
@@ -5367,7 +5353,7 @@
         <v>40626</v>
       </c>
       <c r="C67" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
         <v>51</v>
@@ -5379,16 +5365,16 @@
         <v>9</v>
       </c>
       <c r="G67" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H67" t="s">
         <v>58</v>
       </c>
       <c r="I67" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J67" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s">
         <v>73</v>
@@ -5408,7 +5394,7 @@
         <v>40627</v>
       </c>
       <c r="C68" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D68" t="s">
         <v>55</v>
@@ -5420,16 +5406,16 @@
         <v>9</v>
       </c>
       <c r="G68" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s">
         <v>52</v>
       </c>
       <c r="I68" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J68" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s">
         <v>73</v>
@@ -5449,7 +5435,7 @@
         <v>40628</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D69" t="s">
         <v>51</v>
@@ -5461,16 +5447,16 @@
         <v>9</v>
       </c>
       <c r="G69" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H69" t="s">
         <v>52</v>
       </c>
       <c r="I69" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J69" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K69" t="s">
         <v>73</v>
@@ -5490,7 +5476,7 @@
         <v>40629</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D70" t="s">
         <v>55</v>
@@ -5502,16 +5488,16 @@
         <v>9</v>
       </c>
       <c r="G70" t="s">
+        <v>82</v>
+      </c>
+      <c r="H70" t="s">
+        <v>104</v>
+      </c>
+      <c r="I70" t="s">
+        <v>84</v>
+      </c>
+      <c r="J70" t="s">
         <v>85</v>
-      </c>
-      <c r="H70" t="s">
-        <v>107</v>
-      </c>
-      <c r="I70" t="s">
-        <v>87</v>
-      </c>
-      <c r="J70" t="s">
-        <v>88</v>
       </c>
       <c r="K70" t="s">
         <v>73</v>
@@ -5531,7 +5517,7 @@
         <v>40630</v>
       </c>
       <c r="C71" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D71" t="s">
         <v>51</v>
@@ -5543,16 +5529,16 @@
         <v>9</v>
       </c>
       <c r="G71" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H71" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I71" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J71" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s">
         <v>73</v>
@@ -5572,7 +5558,7 @@
         <v>40631</v>
       </c>
       <c r="C72" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D72" t="s">
         <v>55</v>
@@ -5584,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="G72" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H72" t="s">
         <v>59</v>
       </c>
       <c r="I72" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J72" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K72" t="s">
         <v>73</v>
@@ -5613,7 +5599,7 @@
         <v>40632</v>
       </c>
       <c r="C73" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D73" t="s">
         <v>51</v>
@@ -5625,16 +5611,16 @@
         <v>9</v>
       </c>
       <c r="G73" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s">
         <v>59</v>
       </c>
       <c r="I73" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J73" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K73" t="s">
         <v>73</v>
@@ -5654,7 +5640,7 @@
         <v>40641</v>
       </c>
       <c r="C74" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D74" t="s">
         <v>55</v>
@@ -5666,16 +5652,16 @@
         <v>9</v>
       </c>
       <c r="G74" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s">
         <v>53</v>
       </c>
       <c r="I74" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J74" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K74" t="s">
         <v>73</v>
@@ -5695,7 +5681,7 @@
         <v>40642</v>
       </c>
       <c r="C75" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D75" t="s">
         <v>51</v>
@@ -5707,16 +5693,16 @@
         <v>9</v>
       </c>
       <c r="G75" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H75" t="s">
         <v>53</v>
       </c>
       <c r="I75" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J75" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K75" t="s">
         <v>73</v>
@@ -5736,7 +5722,7 @@
         <v>40643</v>
       </c>
       <c r="C76" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D76" t="s">
         <v>55</v>
@@ -5748,16 +5734,16 @@
         <v>9</v>
       </c>
       <c r="G76" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H76" t="s">
         <v>65</v>
       </c>
       <c r="I76" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J76" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s">
         <v>73</v>
@@ -5777,7 +5763,7 @@
         <v>40644</v>
       </c>
       <c r="C77" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D77" t="s">
         <v>51</v>
@@ -5789,16 +5775,16 @@
         <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H77" t="s">
         <v>65</v>
       </c>
       <c r="I77" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J77" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s">
         <v>73</v>
@@ -5818,7 +5804,7 @@
         <v>40645</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D78" t="s">
         <v>55</v>
@@ -5830,16 +5816,16 @@
         <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H78" t="s">
         <v>58</v>
       </c>
       <c r="I78" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J78" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s">
         <v>73</v>
@@ -5859,7 +5845,7 @@
         <v>40646</v>
       </c>
       <c r="C79" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D79" t="s">
         <v>51</v>
@@ -5871,16 +5857,16 @@
         <v>9</v>
       </c>
       <c r="G79" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H79" t="s">
         <v>58</v>
       </c>
       <c r="I79" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J79" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K79" t="s">
         <v>73</v>
@@ -5900,7 +5886,7 @@
         <v>40647</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D80" t="s">
         <v>55</v>
@@ -5912,16 +5898,16 @@
         <v>9</v>
       </c>
       <c r="G80" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H80" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I80" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J80" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K80" t="s">
         <v>73</v>
@@ -5941,7 +5927,7 @@
         <v>40648</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D81" t="s">
         <v>51</v>
@@ -5953,16 +5939,16 @@
         <v>9</v>
       </c>
       <c r="G81" t="s">
+        <v>86</v>
+      </c>
+      <c r="H81" t="s">
+        <v>101</v>
+      </c>
+      <c r="I81" t="s">
+        <v>88</v>
+      </c>
+      <c r="J81" t="s">
         <v>89</v>
-      </c>
-      <c r="H81" t="s">
-        <v>104</v>
-      </c>
-      <c r="I81" t="s">
-        <v>91</v>
-      </c>
-      <c r="J81" t="s">
-        <v>92</v>
       </c>
       <c r="K81" t="s">
         <v>73</v>
@@ -5982,7 +5968,7 @@
         <v>40649</v>
       </c>
       <c r="C82" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D82" t="s">
         <v>55</v>
@@ -5994,16 +5980,16 @@
         <v>9</v>
       </c>
       <c r="G82" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H82" t="s">
         <v>52</v>
       </c>
       <c r="I82" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J82" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K82" t="s">
         <v>73</v>
@@ -6023,7 +6009,7 @@
         <v>40650</v>
       </c>
       <c r="C83" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D83" t="s">
         <v>51</v>
@@ -6035,16 +6021,16 @@
         <v>9</v>
       </c>
       <c r="G83" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H83" t="s">
         <v>52</v>
       </c>
       <c r="I83" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J83" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K83" t="s">
         <v>73</v>
@@ -6064,7 +6050,7 @@
         <v>40651</v>
       </c>
       <c r="C84" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D84" t="s">
         <v>55</v>
@@ -6076,16 +6062,16 @@
         <v>9</v>
       </c>
       <c r="G84" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I84" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J84" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K84" t="s">
         <v>73</v>
@@ -6105,7 +6091,7 @@
         <v>40652</v>
       </c>
       <c r="C85" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D85" t="s">
         <v>51</v>
@@ -6117,16 +6103,16 @@
         <v>9</v>
       </c>
       <c r="G85" t="s">
+        <v>86</v>
+      </c>
+      <c r="H85" t="s">
+        <v>104</v>
+      </c>
+      <c r="I85" t="s">
+        <v>88</v>
+      </c>
+      <c r="J85" t="s">
         <v>89</v>
-      </c>
-      <c r="H85" t="s">
-        <v>107</v>
-      </c>
-      <c r="I85" t="s">
-        <v>91</v>
-      </c>
-      <c r="J85" t="s">
-        <v>92</v>
       </c>
       <c r="K85" t="s">
         <v>73</v>
@@ -6146,7 +6132,7 @@
         <v>40653</v>
       </c>
       <c r="C86" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D86" t="s">
         <v>55</v>
@@ -6158,16 +6144,16 @@
         <v>9</v>
       </c>
       <c r="G86" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H86" t="s">
         <v>59</v>
       </c>
       <c r="I86" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J86" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K86" t="s">
         <v>73</v>
@@ -6187,7 +6173,7 @@
         <v>40654</v>
       </c>
       <c r="C87" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D87" t="s">
         <v>51</v>
@@ -6199,16 +6185,16 @@
         <v>9</v>
       </c>
       <c r="G87" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H87" t="s">
         <v>59</v>
       </c>
       <c r="I87" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J87" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K87" t="s">
         <v>73</v>
@@ -6228,7 +6214,7 @@
         <v>40669</v>
       </c>
       <c r="C88" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D88" t="s">
         <v>55</v>
@@ -6240,16 +6226,16 @@
         <v>9</v>
       </c>
       <c r="G88" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I88" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J88" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K88" t="s">
         <v>73</v>
@@ -6269,7 +6255,7 @@
         <v>40670</v>
       </c>
       <c r="C89" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D89" t="s">
         <v>51</v>
@@ -6281,16 +6267,16 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H89" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I89" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J89" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s">
         <v>73</v>
@@ -6310,7 +6296,7 @@
         <v>40673</v>
       </c>
       <c r="C90" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D90" t="s">
         <v>55</v>
@@ -6322,16 +6308,16 @@
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H90" t="s">
         <v>52</v>
       </c>
       <c r="I90" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J90" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K90" t="s">
         <v>73</v>
@@ -6351,7 +6337,7 @@
         <v>40674</v>
       </c>
       <c r="C91" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D91" t="s">
         <v>51</v>
@@ -6363,16 +6349,16 @@
         <v>9</v>
       </c>
       <c r="G91" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H91" t="s">
         <v>52</v>
       </c>
       <c r="I91" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J91" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K91" t="s">
         <v>73</v>
@@ -6392,7 +6378,7 @@
         <v>40675</v>
       </c>
       <c r="C92" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D92" t="s">
         <v>55</v>
@@ -6404,16 +6390,16 @@
         <v>9</v>
       </c>
       <c r="G92" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H92" t="s">
         <v>67</v>
       </c>
       <c r="I92" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J92" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K92" t="s">
         <v>73</v>
@@ -6433,7 +6419,7 @@
         <v>40676</v>
       </c>
       <c r="C93" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D93" t="s">
         <v>51</v>
@@ -6445,16 +6431,16 @@
         <v>9</v>
       </c>
       <c r="G93" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H93" t="s">
         <v>67</v>
       </c>
       <c r="I93" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J93" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K93" t="s">
         <v>73</v>
@@ -6474,7 +6460,7 @@
         <v>40679</v>
       </c>
       <c r="C94" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D94" t="s">
         <v>40</v>
@@ -6486,19 +6472,19 @@
         <v>9</v>
       </c>
       <c r="G94" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H94" t="s">
         <v>67</v>
       </c>
       <c r="I94" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J94" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K94" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -6515,7 +6501,7 @@
         <v>40681</v>
       </c>
       <c r="C95" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D95" t="s">
         <v>43</v>
@@ -6527,19 +6513,19 @@
         <v>9</v>
       </c>
       <c r="G95" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H95" t="s">
         <v>64</v>
       </c>
       <c r="I95" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J95" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K95" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -6556,7 +6542,7 @@
         <v>40683</v>
       </c>
       <c r="C96" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D96" t="s">
         <v>46</v>
@@ -6568,19 +6554,19 @@
         <v>9</v>
       </c>
       <c r="G96" t="s">
+        <v>107</v>
+      </c>
+      <c r="H96" t="s">
+        <v>95</v>
+      </c>
+      <c r="I96" t="s">
+        <v>108</v>
+      </c>
+      <c r="J96" t="s">
+        <v>109</v>
+      </c>
+      <c r="K96" t="s">
         <v>110</v>
-      </c>
-      <c r="H96" t="s">
-        <v>98</v>
-      </c>
-      <c r="I96" t="s">
-        <v>111</v>
-      </c>
-      <c r="J96" t="s">
-        <v>112</v>
-      </c>
-      <c r="K96" t="s">
-        <v>113</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -6597,7 +6583,7 @@
         <v>40684</v>
       </c>
       <c r="C97" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D97" t="s">
         <v>46</v>
@@ -6609,19 +6595,19 @@
         <v>9</v>
       </c>
       <c r="G97" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H97" t="s">
         <v>58</v>
       </c>
       <c r="I97" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J97" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K97" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -6638,7 +6624,7 @@
         <v>40685</v>
       </c>
       <c r="C98" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D98" t="s">
         <v>55</v>
@@ -6650,19 +6636,19 @@
         <v>9</v>
       </c>
       <c r="G98" t="s">
+        <v>107</v>
+      </c>
+      <c r="H98" t="s">
+        <v>101</v>
+      </c>
+      <c r="I98" t="s">
+        <v>108</v>
+      </c>
+      <c r="J98" t="s">
+        <v>109</v>
+      </c>
+      <c r="K98" t="s">
         <v>110</v>
-      </c>
-      <c r="H98" t="s">
-        <v>104</v>
-      </c>
-      <c r="I98" t="s">
-        <v>111</v>
-      </c>
-      <c r="J98" t="s">
-        <v>112</v>
-      </c>
-      <c r="K98" t="s">
-        <v>113</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -6679,7 +6665,7 @@
         <v>40686</v>
       </c>
       <c r="C99" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D99" t="s">
         <v>55</v>
@@ -6691,19 +6677,19 @@
         <v>9</v>
       </c>
       <c r="G99" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H99" t="s">
         <v>65</v>
       </c>
       <c r="I99" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J99" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K99" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -6714,16 +6700,16 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B100">
         <v>40687</v>
       </c>
       <c r="C100" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D100" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E100" t="s">
         <v>19</v>
@@ -6732,16 +6718,16 @@
         <v>9</v>
       </c>
       <c r="G100" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H100" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I100" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J100" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K100" t="s">
         <v>73</v>
@@ -6759,16 +6745,16 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B101">
         <v>40688</v>
       </c>
       <c r="C101" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D101" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
@@ -6777,16 +6763,16 @@
         <v>9</v>
       </c>
       <c r="G101" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H101" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I101" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J101" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K101" t="s">
         <v>73</v>
@@ -6798,22 +6784,22 @@
         <v>78</v>
       </c>
       <c r="N101" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O101"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B102">
         <v>40689</v>
       </c>
       <c r="C102" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D102" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E102" t="s">
         <v>19</v>
@@ -6822,16 +6808,16 @@
         <v>9</v>
       </c>
       <c r="G102" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H102" t="s">
         <v>60</v>
       </c>
       <c r="I102" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J102" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K102" t="s">
         <v>73</v>
@@ -6849,16 +6835,16 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B103">
         <v>40690</v>
       </c>
       <c r="C103" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D103" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E103" t="s">
         <v>19</v>
@@ -6867,16 +6853,16 @@
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H103" t="s">
         <v>60</v>
       </c>
       <c r="I103" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J103" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K103" t="s">
         <v>73</v>
@@ -6888,22 +6874,22 @@
         <v>79</v>
       </c>
       <c r="N103" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O103"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B104">
         <v>40691</v>
       </c>
       <c r="C104" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D104" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E104" t="s">
         <v>19</v>
@@ -6912,45 +6898,43 @@
         <v>9</v>
       </c>
       <c r="G104" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H104" t="s">
         <v>60</v>
       </c>
       <c r="I104" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J104" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K104" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L104">
         <v>3</v>
       </c>
-      <c r="M104" t="s">
-        <v>80</v>
-      </c>
+      <c r="M104"/>
       <c r="N104" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O104" t="s">
-        <v>124</v>
+        <v>219</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B105">
         <v>40692</v>
       </c>
       <c r="C105" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D105" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E105" t="s">
         <v>19</v>
@@ -6959,45 +6943,43 @@
         <v>9</v>
       </c>
       <c r="G105" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H105" t="s">
         <v>60</v>
       </c>
       <c r="I105" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J105" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K105" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L105">
         <v>3</v>
       </c>
-      <c r="M105" t="s">
-        <v>80</v>
-      </c>
+      <c r="M105"/>
       <c r="N105" t="s">
         <v>13</v>
       </c>
       <c r="O105" t="s">
-        <v>126</v>
+        <v>220</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B106">
         <v>40693</v>
       </c>
       <c r="C106" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D106" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E106" t="s">
         <v>19</v>
@@ -7006,45 +6988,43 @@
         <v>9</v>
       </c>
       <c r="G106" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H106" t="s">
         <v>60</v>
       </c>
       <c r="I106" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J106" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K106" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L106">
         <v>3</v>
       </c>
-      <c r="M106" t="s">
-        <v>81</v>
-      </c>
+      <c r="M106"/>
       <c r="N106" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O106" t="s">
-        <v>130</v>
+        <v>221</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B107">
         <v>40694</v>
       </c>
       <c r="C107" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D107" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E107" t="s">
         <v>19</v>
@@ -7053,45 +7033,43 @@
         <v>9</v>
       </c>
       <c r="G107" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H107" t="s">
         <v>60</v>
       </c>
       <c r="I107" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J107" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K107" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L107">
         <v>3</v>
       </c>
-      <c r="M107" t="s">
-        <v>81</v>
-      </c>
+      <c r="M107"/>
       <c r="N107" t="s">
         <v>13</v>
       </c>
       <c r="O107" t="s">
-        <v>133</v>
+        <v>222</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B108">
         <v>40695</v>
       </c>
       <c r="C108" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D108" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E108" t="s">
         <v>19</v>
@@ -7100,45 +7078,43 @@
         <v>9</v>
       </c>
       <c r="G108" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H108" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I108" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J108" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K108" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L108">
         <v>3</v>
       </c>
-      <c r="M108" t="s">
-        <v>135</v>
-      </c>
+      <c r="M108"/>
       <c r="N108" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O108" t="s">
-        <v>136</v>
+        <v>223</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B109">
         <v>40696</v>
       </c>
       <c r="C109" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D109" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E109" t="s">
         <v>19</v>
@@ -7147,45 +7123,43 @@
         <v>9</v>
       </c>
       <c r="G109" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H109" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I109" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J109" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K109" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L109">
         <v>3</v>
       </c>
-      <c r="M109" t="s">
-        <v>137</v>
-      </c>
+      <c r="M109"/>
       <c r="N109" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O109" t="s">
-        <v>138</v>
+        <v>224</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B110">
         <v>40697</v>
       </c>
       <c r="C110" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D110" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E110" t="s">
         <v>19</v>
@@ -7194,45 +7168,43 @@
         <v>9</v>
       </c>
       <c r="G110" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H110" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I110" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J110" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K110" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L110">
         <v>3</v>
       </c>
-      <c r="M110" t="s">
-        <v>135</v>
-      </c>
+      <c r="M110"/>
       <c r="N110" t="s">
         <v>13</v>
       </c>
       <c r="O110" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B111">
         <v>40698</v>
       </c>
       <c r="C111" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D111" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
@@ -7241,45 +7213,43 @@
         <v>9</v>
       </c>
       <c r="G111" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H111" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I111" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J111" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K111" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L111">
         <v>3</v>
       </c>
-      <c r="M111" t="s">
-        <v>137</v>
-      </c>
+      <c r="M111"/>
       <c r="N111" t="s">
         <v>13</v>
       </c>
       <c r="O111" t="s">
-        <v>140</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B112">
         <v>40699</v>
       </c>
       <c r="C112" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D112" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -7288,43 +7258,43 @@
         <v>9</v>
       </c>
       <c r="G112" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H112" t="s">
         <v>66</v>
       </c>
       <c r="I112" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J112" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K112" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L112">
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="N112" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O112"/>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B113">
         <v>40700</v>
       </c>
       <c r="C113" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D113" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -7333,25 +7303,25 @@
         <v>9</v>
       </c>
       <c r="G113" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H113" t="s">
         <v>66</v>
       </c>
       <c r="I113" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J113" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="K113" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L113">
         <v>3</v>
       </c>
       <c r="M113" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="N113" t="s">
         <v>13</v>
@@ -7378,16 +7348,16 @@
         <v>9</v>
       </c>
       <c r="G114" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H114" t="s">
         <v>10</v>
       </c>
       <c r="I114" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J114" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K114" t="s">
         <v>73</v>
@@ -7396,7 +7366,7 @@
         <v>6</v>
       </c>
       <c r="M114" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="N114" t="s">
         <v>13</v>
@@ -7423,16 +7393,16 @@
         <v>9</v>
       </c>
       <c r="G115" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H115" t="s">
         <v>10</v>
       </c>
       <c r="I115" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J115" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K115" t="s">
         <v>73</v>
@@ -7441,10 +7411,10 @@
         <v>6</v>
       </c>
       <c r="M115" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="N115" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="O115"/>
     </row>
@@ -7468,16 +7438,16 @@
         <v>9</v>
       </c>
       <c r="G116" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H116" t="s">
         <v>10</v>
       </c>
       <c r="I116" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J116" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K116" t="s">
         <v>73</v>
@@ -7486,10 +7456,10 @@
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="N116" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O116"/>
     </row>
@@ -7513,16 +7483,16 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H117" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I117" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J117" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K117" t="s">
         <v>73</v>
@@ -7531,7 +7501,7 @@
         <v>6</v>
       </c>
       <c r="M117" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="N117" t="s">
         <v>13</v>
@@ -7558,16 +7528,16 @@
         <v>9</v>
       </c>
       <c r="G118" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H118" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I118" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J118" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K118" t="s">
         <v>73</v>
@@ -7576,10 +7546,10 @@
         <v>6</v>
       </c>
       <c r="M118" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="N118" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="O118"/>
     </row>
@@ -7603,16 +7573,16 @@
         <v>9</v>
       </c>
       <c r="G119" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H119" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I119" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J119" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K119" t="s">
         <v>73</v>
@@ -7621,16 +7591,16 @@
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="N119" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O119"/>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B120">
         <v>40707</v>
@@ -7639,7 +7609,7 @@
         <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="E120" t="s">
         <v>19</v>
@@ -7648,16 +7618,16 @@
         <v>9</v>
       </c>
       <c r="G120" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H120" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I120" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J120" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K120" t="s">
         <v>73</v>
@@ -7666,7 +7636,7 @@
         <v>6</v>
       </c>
       <c r="M120" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="N120" t="s">
         <v>13</v>
@@ -7675,7 +7645,7 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B121">
         <v>40708</v>
@@ -7684,7 +7654,7 @@
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
@@ -7693,16 +7663,16 @@
         <v>9</v>
       </c>
       <c r="G121" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H121" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I121" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J121" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K121" t="s">
         <v>73</v>
@@ -7711,16 +7681,16 @@
         <v>6</v>
       </c>
       <c r="M121" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="N121" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="O121"/>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B122">
         <v>40709</v>
@@ -7729,7 +7699,7 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E122" t="s">
         <v>19</v>
@@ -7738,16 +7708,16 @@
         <v>9</v>
       </c>
       <c r="G122" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H122" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I122" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J122" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K122" t="s">
         <v>73</v>
@@ -7756,16 +7726,16 @@
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="N122" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O122"/>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B123">
         <v>40710</v>
@@ -7774,7 +7744,7 @@
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -7783,16 +7753,16 @@
         <v>9</v>
       </c>
       <c r="G123" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H123" t="s">
         <v>10</v>
       </c>
       <c r="I123" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J123" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K123" t="s">
         <v>73</v>
@@ -7801,7 +7771,7 @@
         <v>6</v>
       </c>
       <c r="M123" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="N123" t="s">
         <v>13</v>
@@ -7810,7 +7780,7 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B124">
         <v>40711</v>
@@ -7819,7 +7789,7 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -7828,16 +7798,16 @@
         <v>9</v>
       </c>
       <c r="G124" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H124" t="s">
         <v>10</v>
       </c>
       <c r="I124" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J124" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K124" t="s">
         <v>73</v>
@@ -7846,16 +7816,16 @@
         <v>6</v>
       </c>
       <c r="M124" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="N124" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="O124"/>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B125">
         <v>40712</v>
@@ -7864,7 +7834,7 @@
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -7873,16 +7843,16 @@
         <v>9</v>
       </c>
       <c r="G125" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H125" t="s">
         <v>10</v>
       </c>
       <c r="I125" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J125" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K125" t="s">
         <v>73</v>
@@ -7891,16 +7861,16 @@
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="N125" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O125"/>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="B126">
         <v>40713</v>
@@ -7909,7 +7879,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="E126" t="s">
         <v>19</v>
@@ -7918,16 +7888,16 @@
         <v>9</v>
       </c>
       <c r="G126" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H126" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I126" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J126" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K126" t="s">
         <v>73</v>
@@ -7936,7 +7906,7 @@
         <v>6</v>
       </c>
       <c r="M126" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="N126" t="s">
         <v>13</v>
@@ -7945,7 +7915,7 @@
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="B127">
         <v>40714</v>
@@ -7954,7 +7924,7 @@
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="E127" t="s">
         <v>19</v>
@@ -7963,16 +7933,16 @@
         <v>9</v>
       </c>
       <c r="G127" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H127" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I127" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J127" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K127" t="s">
         <v>73</v>
@@ -7981,16 +7951,16 @@
         <v>6</v>
       </c>
       <c r="M127" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="N127" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="O127"/>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="B128">
         <v>40715</v>
@@ -7999,7 +7969,7 @@
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="E128" t="s">
         <v>19</v>
@@ -8008,16 +7978,16 @@
         <v>9</v>
       </c>
       <c r="G128" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H128" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I128" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J128" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K128" t="s">
         <v>73</v>
@@ -8026,16 +7996,16 @@
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="N128" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O128"/>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="B129">
         <v>40716</v>
@@ -8044,7 +8014,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -8053,16 +8023,16 @@
         <v>9</v>
       </c>
       <c r="G129" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H129" t="s">
         <v>10</v>
       </c>
       <c r="I129" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J129" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K129" t="s">
         <v>73</v>
@@ -8071,7 +8041,7 @@
         <v>6</v>
       </c>
       <c r="M129" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="N129" t="s">
         <v>13</v>
@@ -8080,7 +8050,7 @@
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="B130">
         <v>40717</v>
@@ -8089,7 +8059,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -8098,16 +8068,16 @@
         <v>9</v>
       </c>
       <c r="G130" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H130" t="s">
         <v>10</v>
       </c>
       <c r="I130" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J130" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K130" t="s">
         <v>73</v>
@@ -8116,16 +8086,16 @@
         <v>6</v>
       </c>
       <c r="M130" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="N130" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="O130"/>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B131">
         <v>40718</v>
@@ -8134,7 +8104,7 @@
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -8143,16 +8113,16 @@
         <v>9</v>
       </c>
       <c r="G131" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H131" t="s">
         <v>10</v>
       </c>
       <c r="I131" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J131" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K131" t="s">
         <v>73</v>
@@ -8161,16 +8131,16 @@
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="N131" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O131"/>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="B132">
         <v>40719</v>
@@ -8179,7 +8149,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -8188,16 +8158,16 @@
         <v>9</v>
       </c>
       <c r="G132" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H132" t="s">
         <v>10</v>
       </c>
       <c r="I132" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J132" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K132" t="s">
         <v>73</v>
@@ -8206,16 +8176,16 @@
         <v>6</v>
       </c>
       <c r="M132" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="N132" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="O132"/>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="B133">
         <v>40720</v>
@@ -8224,7 +8194,7 @@
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -8233,16 +8203,16 @@
         <v>9</v>
       </c>
       <c r="G133" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H133" t="s">
         <v>10</v>
       </c>
       <c r="I133" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J133" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K133" t="s">
         <v>73</v>
@@ -8251,10 +8221,10 @@
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="N133" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O133"/>
     </row>
@@ -8278,16 +8248,16 @@
         <v>9</v>
       </c>
       <c r="G134" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H134" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="I134" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J134" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K134" t="s">
         <v>73</v>
@@ -8296,7 +8266,7 @@
         <v>6</v>
       </c>
       <c r="M134" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="N134" t="s">
         <v>13</v>
@@ -8323,16 +8293,16 @@
         <v>9</v>
       </c>
       <c r="G135" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H135" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="I135" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J135" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K135" t="s">
         <v>73</v>
@@ -8341,10 +8311,10 @@
         <v>6</v>
       </c>
       <c r="M135" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="N135" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="O135"/>
     </row>
@@ -8368,16 +8338,16 @@
         <v>9</v>
       </c>
       <c r="G136" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H136" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="I136" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J136" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K136" t="s">
         <v>73</v>
@@ -8386,16 +8356,16 @@
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="N136" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O136"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="B137">
         <v>40728</v>
@@ -8404,7 +8374,7 @@
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="E137" t="s">
         <v>19</v>
@@ -8413,16 +8383,16 @@
         <v>9</v>
       </c>
       <c r="G137" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H137" t="s">
         <v>20</v>
       </c>
       <c r="I137" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J137" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K137" t="s">
         <v>73</v>
@@ -8431,7 +8401,7 @@
         <v>6</v>
       </c>
       <c r="M137" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="N137" t="s">
         <v>13</v>
@@ -8440,7 +8410,7 @@
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B138">
         <v>40729</v>
@@ -8449,7 +8419,7 @@
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E138" t="s">
         <v>19</v>
@@ -8458,16 +8428,16 @@
         <v>9</v>
       </c>
       <c r="G138" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H138" t="s">
         <v>20</v>
       </c>
       <c r="I138" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J138" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K138" t="s">
         <v>73</v>
@@ -8476,16 +8446,16 @@
         <v>6</v>
       </c>
       <c r="M138" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="N138" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="O138"/>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="B139">
         <v>40730</v>
@@ -8494,7 +8464,7 @@
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="E139" t="s">
         <v>19</v>
@@ -8503,16 +8473,16 @@
         <v>9</v>
       </c>
       <c r="G139" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H139" t="s">
         <v>20</v>
       </c>
       <c r="I139" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J139" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K139" t="s">
         <v>73</v>
@@ -8521,16 +8491,16 @@
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="N139" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O139"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="B140">
         <v>40731</v>
@@ -8539,7 +8509,7 @@
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E140" t="s">
         <v>19</v>
@@ -8548,16 +8518,16 @@
         <v>9</v>
       </c>
       <c r="G140" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H140" t="s">
         <v>47</v>
       </c>
       <c r="I140" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J140" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K140" t="s">
         <v>73</v>
@@ -8566,7 +8536,7 @@
         <v>6</v>
       </c>
       <c r="M140" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="N140" t="s">
         <v>13</v>
@@ -8575,7 +8545,7 @@
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="B141">
         <v>40732</v>
@@ -8584,7 +8554,7 @@
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E141" t="s">
         <v>19</v>
@@ -8593,16 +8563,16 @@
         <v>9</v>
       </c>
       <c r="G141" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H141" t="s">
         <v>47</v>
       </c>
       <c r="I141" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J141" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K141" t="s">
         <v>73</v>
@@ -8611,16 +8581,16 @@
         <v>6</v>
       </c>
       <c r="M141" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="N141" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="O141"/>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B142">
         <v>40733</v>
@@ -8629,7 +8599,7 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E142" t="s">
         <v>19</v>
@@ -8638,16 +8608,16 @@
         <v>9</v>
       </c>
       <c r="G142" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H142" t="s">
         <v>47</v>
       </c>
       <c r="I142" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J142" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K142" t="s">
         <v>73</v>
@@ -8656,16 +8626,16 @@
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="N142" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O142"/>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B143">
         <v>40734</v>
@@ -8674,7 +8644,7 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E143" t="s">
         <v>19</v>
@@ -8683,16 +8653,16 @@
         <v>9</v>
       </c>
       <c r="G143" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H143" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="I143" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J143" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K143" t="s">
         <v>73</v>
@@ -8701,7 +8671,7 @@
         <v>6</v>
       </c>
       <c r="M143" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="N143" t="s">
         <v>13</v>
@@ -8710,7 +8680,7 @@
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B144">
         <v>40735</v>
@@ -8719,7 +8689,7 @@
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E144" t="s">
         <v>19</v>
@@ -8728,16 +8698,16 @@
         <v>9</v>
       </c>
       <c r="G144" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H144" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="I144" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J144" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K144" t="s">
         <v>73</v>
@@ -8746,16 +8716,16 @@
         <v>6</v>
       </c>
       <c r="M144" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="N144" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="O144"/>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B145">
         <v>40736</v>
@@ -8764,7 +8734,7 @@
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="E145" t="s">
         <v>19</v>
@@ -8773,16 +8743,16 @@
         <v>9</v>
       </c>
       <c r="G145" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H145" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="I145" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J145" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K145" t="s">
         <v>73</v>
@@ -8791,16 +8761,16 @@
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="N145" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O145"/>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="B146">
         <v>40737</v>
@@ -8809,7 +8779,7 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="E146" t="s">
         <v>19</v>
@@ -8818,16 +8788,16 @@
         <v>9</v>
       </c>
       <c r="G146" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H146" t="s">
         <v>20</v>
       </c>
       <c r="I146" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J146" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K146" t="s">
         <v>73</v>
@@ -8836,7 +8806,7 @@
         <v>6</v>
       </c>
       <c r="M146" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="N146" t="s">
         <v>13</v>
@@ -8845,7 +8815,7 @@
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B147">
         <v>40738</v>
@@ -8854,7 +8824,7 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="E147" t="s">
         <v>19</v>
@@ -8863,16 +8833,16 @@
         <v>9</v>
       </c>
       <c r="G147" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H147" t="s">
         <v>20</v>
       </c>
       <c r="I147" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J147" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K147" t="s">
         <v>73</v>
@@ -8881,16 +8851,16 @@
         <v>6</v>
       </c>
       <c r="M147" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="N147" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="O147"/>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="B148">
         <v>40739</v>
@@ -8899,7 +8869,7 @@
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E148" t="s">
         <v>19</v>
@@ -8908,16 +8878,16 @@
         <v>9</v>
       </c>
       <c r="G148" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H148" t="s">
         <v>20</v>
       </c>
       <c r="I148" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J148" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K148" t="s">
         <v>73</v>
@@ -8926,10 +8896,10 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="N148" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O148"/>
     </row>
@@ -8953,16 +8923,16 @@
         <v>9</v>
       </c>
       <c r="G149" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H149" t="s">
         <v>28</v>
       </c>
       <c r="I149" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J149" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K149" t="s">
         <v>73</v>
@@ -8971,7 +8941,7 @@
         <v>6</v>
       </c>
       <c r="M149" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="N149" t="s">
         <v>13</v>
@@ -8998,16 +8968,16 @@
         <v>9</v>
       </c>
       <c r="G150" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H150" t="s">
         <v>28</v>
       </c>
       <c r="I150" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J150" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K150" t="s">
         <v>73</v>
@@ -9016,10 +8986,10 @@
         <v>6</v>
       </c>
       <c r="M150" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="N150" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="O150"/>
     </row>
@@ -9043,16 +9013,16 @@
         <v>9</v>
       </c>
       <c r="G151" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H151" t="s">
         <v>28</v>
       </c>
       <c r="I151" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J151" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K151" t="s">
         <v>73</v>
@@ -9061,10 +9031,10 @@
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="N151" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O151"/>
     </row>
@@ -9088,16 +9058,16 @@
         <v>9</v>
       </c>
       <c r="G152" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H152" t="s">
         <v>28</v>
       </c>
       <c r="I152" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J152" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K152" t="s">
         <v>73</v>
@@ -9106,7 +9076,7 @@
         <v>6</v>
       </c>
       <c r="M152" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="N152" t="s">
         <v>13</v>
@@ -9133,16 +9103,16 @@
         <v>9</v>
       </c>
       <c r="G153" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H153" t="s">
         <v>28</v>
       </c>
       <c r="I153" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J153" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K153" t="s">
         <v>73</v>
@@ -9151,10 +9121,10 @@
         <v>6</v>
       </c>
       <c r="M153" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="N153" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="O153"/>
     </row>
@@ -9178,16 +9148,16 @@
         <v>9</v>
       </c>
       <c r="G154" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H154" t="s">
         <v>28</v>
       </c>
       <c r="I154" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J154" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K154" t="s">
         <v>73</v>
@@ -9196,16 +9166,16 @@
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="N154" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O154"/>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B155">
         <v>40749</v>
@@ -9214,7 +9184,7 @@
         <v>26</v>
       </c>
       <c r="D155" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E155" t="s">
         <v>19</v>
@@ -9223,16 +9193,16 @@
         <v>9</v>
       </c>
       <c r="G155" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H155" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I155" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J155" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K155" t="s">
         <v>73</v>
@@ -9241,7 +9211,7 @@
         <v>6</v>
       </c>
       <c r="M155" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="N155" t="s">
         <v>13</v>
@@ -9250,7 +9220,7 @@
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="B156">
         <v>40750</v>
@@ -9259,7 +9229,7 @@
         <v>26</v>
       </c>
       <c r="D156" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="E156" t="s">
         <v>19</v>
@@ -9268,16 +9238,16 @@
         <v>9</v>
       </c>
       <c r="G156" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H156" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I156" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J156" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K156" t="s">
         <v>73</v>
@@ -9286,16 +9256,16 @@
         <v>6</v>
       </c>
       <c r="M156" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="N156" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="O156"/>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="B157">
         <v>40751</v>
@@ -9304,7 +9274,7 @@
         <v>26</v>
       </c>
       <c r="D157" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="E157" t="s">
         <v>19</v>
@@ -9313,16 +9283,16 @@
         <v>9</v>
       </c>
       <c r="G157" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H157" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I157" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J157" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K157" t="s">
         <v>73</v>
@@ -9331,16 +9301,16 @@
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="N157" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O157"/>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B158">
         <v>40752</v>
@@ -9349,7 +9319,7 @@
         <v>26</v>
       </c>
       <c r="D158" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E158" t="s">
         <v>19</v>
@@ -9358,16 +9328,16 @@
         <v>9</v>
       </c>
       <c r="G158" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H158" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I158" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J158" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K158" t="s">
         <v>73</v>
@@ -9376,7 +9346,7 @@
         <v>6</v>
       </c>
       <c r="M158" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="N158" t="s">
         <v>13</v>
@@ -9385,7 +9355,7 @@
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="B159">
         <v>40753</v>
@@ -9394,7 +9364,7 @@
         <v>26</v>
       </c>
       <c r="D159" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E159" t="s">
         <v>19</v>
@@ -9403,16 +9373,16 @@
         <v>9</v>
       </c>
       <c r="G159" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H159" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I159" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J159" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K159" t="s">
         <v>73</v>
@@ -9421,16 +9391,16 @@
         <v>6</v>
       </c>
       <c r="M159" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="N159" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="O159"/>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B160">
         <v>40754</v>
@@ -9439,7 +9409,7 @@
         <v>26</v>
       </c>
       <c r="D160" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="E160" t="s">
         <v>19</v>
@@ -9448,16 +9418,16 @@
         <v>9</v>
       </c>
       <c r="G160" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H160" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I160" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J160" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K160" t="s">
         <v>73</v>
@@ -9466,16 +9436,16 @@
         <v>0</v>
       </c>
       <c r="M160" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="N160" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O160"/>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="B161">
         <v>40755</v>
@@ -9484,7 +9454,7 @@
         <v>26</v>
       </c>
       <c r="D161" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="E161" t="s">
         <v>19</v>
@@ -9493,16 +9463,16 @@
         <v>9</v>
       </c>
       <c r="G161" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H161" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="I161" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J161" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K161" t="s">
         <v>73</v>
@@ -9511,7 +9481,7 @@
         <v>6</v>
       </c>
       <c r="M161" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N161" t="s">
         <v>13</v>
@@ -9520,7 +9490,7 @@
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="B162">
         <v>40756</v>
@@ -9529,7 +9499,7 @@
         <v>26</v>
       </c>
       <c r="D162" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="E162" t="s">
         <v>19</v>
@@ -9538,16 +9508,16 @@
         <v>9</v>
       </c>
       <c r="G162" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H162" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="I162" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J162" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K162" t="s">
         <v>73</v>
@@ -9556,16 +9526,16 @@
         <v>6</v>
       </c>
       <c r="M162" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N162" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="O162"/>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="B163">
         <v>40757</v>
@@ -9574,7 +9544,7 @@
         <v>26</v>
       </c>
       <c r="D163" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="E163" t="s">
         <v>19</v>
@@ -9583,16 +9553,16 @@
         <v>9</v>
       </c>
       <c r="G163" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H163" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="I163" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J163" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K163" t="s">
         <v>73</v>
@@ -9601,10 +9571,10 @@
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N163" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O163"/>
     </row>
@@ -9733,6 +9703,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -9933,27 +9923,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9970,23 +9959,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/202660_UAX_OfertaLenguas.xlsx
+++ b/202660_UAX_OfertaLenguas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202660/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{2F2356BF-5FED-4956-B6D5-A4DB07EC43D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D697DB6-0142-44D4-8FA0-2382541B75C0}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{2F2356BF-5FED-4956-B6D5-A4DB07EC43D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9403812-D451-497E-BF33-B33AB4B06439}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
@@ -16,23 +16,10 @@
     <sheet name="Table1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Slicer_CréditosAcadémicos">#N/A</definedName>
-    <definedName name="Slicer_Método_de_instrucción">#N/A</definedName>
-    <definedName name="Slicer_Notas">#N/A</definedName>
     <definedName name="TabellaUno">Table1!$A$1:$U$5</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
-      <x14:workbookPr/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
-      <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicerCache r:id="rId2"/>
-        <x14:slicerCache r:id="rId3"/>
-        <x14:slicerCache r:id="rId4"/>
-      </x15:slicerCaches>
-    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -52,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="226">
   <si>
     <t>NRC</t>
   </si>
@@ -430,9 +417,6 @@
   </si>
   <si>
     <t>TIDI0302</t>
-  </si>
-  <si>
-    <t>English grammar</t>
   </si>
   <si>
     <t>García Pérez Alfredo</t>
@@ -1979,299 +1963,16 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>1373569</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>27709</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>3212761</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>27709</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-      <mc:Choice Requires="sle15">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="4" name="Método de instrucción">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBB74E13-D684-F730-77F4-115B17329C1F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Método de instrucción"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14603690" y="27709"/>
-              <a:ext cx="1834795" cy="2667000"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1100"/>
-                <a:t>This shape represents a table slicer. Table slicers are not supported in this version of Excel.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2007 or earlier, the slicer can't be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>3297619</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>36368</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>107610</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>36368</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-      <mc:Choice Requires="sle15">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="5" name="CréditosAcadémicos">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8F280EF-B0C3-2A1D-96BC-13D2FCAD93F6}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="CréditosAcadémicos"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="16523343" y="36368"/>
-              <a:ext cx="1834795" cy="2667000"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1100"/>
-                <a:t>This shape represents a table slicer. Table slicers are not supported in this version of Excel.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2007 or earlier, the slicer can't be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>193935</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>45027</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>204326</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>45027</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-      <mc:Choice Requires="sle15">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="6" name="Notas">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC896CF8-4F90-5751-F0C3-B191FAF0FAE9}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Notas"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="18442998" y="45027"/>
-              <a:ext cx="1834795" cy="2667000"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1100"/>
-                <a:t>This shape represents a table slicer. Table slicers are not supported in this version of Excel.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2007 or earlier, the slicer can't be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
-<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Método_de_instrucción" xr10:uid="{03F1D03D-BB1E-40EA-87DF-1313DFC6A3BE}" sourceName="MetodoInstruccion">
-  <extLst>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
-      <x15:tableSlicerCache tableId="1" column="5"/>
-    </x:ext>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{470722E0-AACD-4C17-9CDC-17EF765DBC7E}">
-      <x15:slicerCacheHideItemsWithNoData/>
-    </x:ext>
-  </extLst>
-</slicerCacheDefinition>
-</file>
-
-<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_CréditosAcadémicos" xr10:uid="{66B2CB06-4FFA-41D2-AAC6-DB55BA81D63F}" sourceName="CreditosAcademicos">
-  <extLst>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
-      <x15:tableSlicerCache tableId="1" column="11"/>
-    </x:ext>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{470722E0-AACD-4C17-9CDC-17EF765DBC7E}">
-      <x15:slicerCacheHideItemsWithNoData/>
-    </x:ext>
-  </extLst>
-</slicerCacheDefinition>
-</file>
-
-<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Notas" xr10:uid="{A950D836-A207-4747-B671-20AB0985F092}" sourceName="Notas">
-  <extLst>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
-      <x15:tableSlicerCache tableId="1" column="12"/>
-    </x:ext>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{470722E0-AACD-4C17-9CDC-17EF765DBC7E}">
-      <x15:slicerCacheHideItemsWithNoData/>
-    </x:ext>
-  </extLst>
-</slicerCacheDefinition>
-</file>
-
-<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Método de instrucción" xr10:uid="{2BC91C30-B92F-41C8-A730-5BB649A8D2E3}" cache="Slicer_Método_de_instrucción" caption="MetodoInstruccion" style="SlicerStyleLight2" rowHeight="257175"/>
-  <slicer name="CréditosAcadémicos" xr10:uid="{F47C21A8-22E7-48B9-BF81-DCCDDAB8762E}" cache="Slicer_CréditosAcadémicos" caption="CreditosAcademicos" style="SlicerStyleLight2" rowHeight="257175"/>
-  <slicer name="Notas" xr10:uid="{83F00312-E2A8-4C59-B217-F4FA4D9E1E9B}" cache="Slicer_Notas" caption="Notas" style="SlicerStyleLight2" rowHeight="257175"/>
-</slicers>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:O163" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
-  <autoFilter ref="A1:O163" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
+  <autoFilter ref="A1:O163" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="English academic purposes"/>
+        <filter val="English Grammar"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O163">
     <sortCondition ref="B1:B163"/>
   </sortState>
@@ -2619,7 +2320,7 @@
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="7.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -2680,7 +2381,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -2721,7 +2422,7 @@
       <c r="N2"/>
       <c r="O2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -2762,7 +2463,7 @@
       <c r="N3"/>
       <c r="O3"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -2803,7 +2504,7 @@
       <c r="N4"/>
       <c r="O4"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -2844,7 +2545,7 @@
       <c r="N5"/>
       <c r="O5"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -2885,7 +2586,7 @@
       <c r="N6"/>
       <c r="O6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>56</v>
       </c>
@@ -2926,7 +2627,7 @@
       <c r="N7"/>
       <c r="O7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -2967,7 +2668,7 @@
       <c r="N8"/>
       <c r="O8"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -3008,7 +2709,7 @@
       <c r="N9"/>
       <c r="O9"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -3049,7 +2750,7 @@
       <c r="N10"/>
       <c r="O10"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -3090,7 +2791,7 @@
       <c r="N11"/>
       <c r="O11"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -3131,7 +2832,7 @@
       <c r="N12"/>
       <c r="O12"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -3172,7 +2873,7 @@
       <c r="N13"/>
       <c r="O13"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -3213,7 +2914,7 @@
       <c r="N14"/>
       <c r="O14"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -3254,7 +2955,7 @@
       <c r="N15"/>
       <c r="O15"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -3295,7 +2996,7 @@
       <c r="N16"/>
       <c r="O16"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -3336,7 +3037,7 @@
       <c r="N17"/>
       <c r="O17"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -3377,7 +3078,7 @@
       <c r="N18"/>
       <c r="O18"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -3418,7 +3119,7 @@
       <c r="N19"/>
       <c r="O19"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -3459,7 +3160,7 @@
       <c r="N20"/>
       <c r="O20"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>62</v>
       </c>
@@ -3500,7 +3201,7 @@
       <c r="N21"/>
       <c r="O21"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3541,7 +3242,7 @@
       <c r="N22"/>
       <c r="O22"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -3582,7 +3283,7 @@
       <c r="N23"/>
       <c r="O23"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -3623,7 +3324,7 @@
       <c r="N24"/>
       <c r="O24"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -3664,7 +3365,7 @@
       <c r="N25"/>
       <c r="O25"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -3705,7 +3406,7 @@
       <c r="N26"/>
       <c r="O26"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -3746,7 +3447,7 @@
       <c r="N27"/>
       <c r="O27"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -3787,7 +3488,7 @@
       <c r="N28"/>
       <c r="O28"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -3828,7 +3529,7 @@
       <c r="N29"/>
       <c r="O29"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -3869,7 +3570,7 @@
       <c r="N30"/>
       <c r="O30"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>62</v>
       </c>
@@ -3910,7 +3611,7 @@
       <c r="N31"/>
       <c r="O31"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -3951,7 +3652,7 @@
       <c r="N32"/>
       <c r="O32"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -3992,7 +3693,7 @@
       <c r="N33"/>
       <c r="O33"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -4033,7 +3734,7 @@
       <c r="N34"/>
       <c r="O34"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -4074,7 +3775,7 @@
       <c r="N35"/>
       <c r="O35"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -4115,7 +3816,7 @@
       <c r="N36"/>
       <c r="O36"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>48</v>
       </c>
@@ -4156,7 +3857,7 @@
       <c r="N37"/>
       <c r="O37"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -4197,7 +3898,7 @@
       <c r="N38"/>
       <c r="O38"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -4238,7 +3939,7 @@
       <c r="N39"/>
       <c r="O39"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -4279,7 +3980,7 @@
       <c r="N40"/>
       <c r="O40"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -4320,7 +4021,7 @@
       <c r="N41"/>
       <c r="O41"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -4361,7 +4062,7 @@
       <c r="N42"/>
       <c r="O42"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -4402,7 +4103,7 @@
       <c r="N43"/>
       <c r="O43"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -4443,7 +4144,7 @@
       <c r="N44"/>
       <c r="O44"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -4484,7 +4185,7 @@
       <c r="N45"/>
       <c r="O45"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -4525,7 +4226,7 @@
       <c r="N46"/>
       <c r="O46"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -4566,7 +4267,7 @@
       <c r="N47"/>
       <c r="O47"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>45</v>
       </c>
@@ -4607,7 +4308,7 @@
       <c r="N48"/>
       <c r="O48"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -4648,7 +4349,7 @@
       <c r="N49"/>
       <c r="O49"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>45</v>
       </c>
@@ -4689,7 +4390,7 @@
       <c r="N50"/>
       <c r="O50"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>48</v>
       </c>
@@ -4730,7 +4431,7 @@
       <c r="N51"/>
       <c r="O51"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -4771,7 +4472,7 @@
       <c r="N52"/>
       <c r="O52"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -4812,7 +4513,7 @@
       <c r="N53"/>
       <c r="O53"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>45</v>
       </c>
@@ -4853,7 +4554,7 @@
       <c r="N54"/>
       <c r="O54"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>48</v>
       </c>
@@ -4894,7 +4595,7 @@
       <c r="N55"/>
       <c r="O55"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>45</v>
       </c>
@@ -4935,7 +4636,7 @@
       <c r="N56"/>
       <c r="O56"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>48</v>
       </c>
@@ -4976,7 +4677,7 @@
       <c r="N57"/>
       <c r="O57"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>45</v>
       </c>
@@ -5017,7 +4718,7 @@
       <c r="N58"/>
       <c r="O58"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>48</v>
       </c>
@@ -5058,7 +4759,7 @@
       <c r="N59"/>
       <c r="O59"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>54</v>
       </c>
@@ -5099,7 +4800,7 @@
       <c r="N60"/>
       <c r="O60"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -5140,7 +4841,7 @@
       <c r="N61"/>
       <c r="O61"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>54</v>
       </c>
@@ -5181,7 +4882,7 @@
       <c r="N62"/>
       <c r="O62"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>50</v>
       </c>
@@ -5222,7 +4923,7 @@
       <c r="N63"/>
       <c r="O63"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>54</v>
       </c>
@@ -5263,7 +4964,7 @@
       <c r="N64"/>
       <c r="O64"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>50</v>
       </c>
@@ -5304,7 +5005,7 @@
       <c r="N65"/>
       <c r="O65"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>54</v>
       </c>
@@ -5345,7 +5046,7 @@
       <c r="N66"/>
       <c r="O66"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>50</v>
       </c>
@@ -5386,7 +5087,7 @@
       <c r="N67"/>
       <c r="O67"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>54</v>
       </c>
@@ -5427,7 +5128,7 @@
       <c r="N68"/>
       <c r="O68"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>50</v>
       </c>
@@ -5468,7 +5169,7 @@
       <c r="N69"/>
       <c r="O69"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>54</v>
       </c>
@@ -5509,7 +5210,7 @@
       <c r="N70"/>
       <c r="O70"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>50</v>
       </c>
@@ -5550,7 +5251,7 @@
       <c r="N71"/>
       <c r="O71"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>54</v>
       </c>
@@ -5591,7 +5292,7 @@
       <c r="N72"/>
       <c r="O72"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>50</v>
       </c>
@@ -5632,7 +5333,7 @@
       <c r="N73"/>
       <c r="O73"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>54</v>
       </c>
@@ -5673,7 +5374,7 @@
       <c r="N74"/>
       <c r="O74"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>50</v>
       </c>
@@ -5714,7 +5415,7 @@
       <c r="N75"/>
       <c r="O75"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>54</v>
       </c>
@@ -5755,7 +5456,7 @@
       <c r="N76"/>
       <c r="O76"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>50</v>
       </c>
@@ -5796,7 +5497,7 @@
       <c r="N77"/>
       <c r="O77"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>54</v>
       </c>
@@ -5837,7 +5538,7 @@
       <c r="N78"/>
       <c r="O78"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>50</v>
       </c>
@@ -5878,7 +5579,7 @@
       <c r="N79"/>
       <c r="O79"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>54</v>
       </c>
@@ -5919,7 +5620,7 @@
       <c r="N80"/>
       <c r="O80"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>50</v>
       </c>
@@ -5960,7 +5661,7 @@
       <c r="N81"/>
       <c r="O81"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>54</v>
       </c>
@@ -6001,7 +5702,7 @@
       <c r="N82"/>
       <c r="O82"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>50</v>
       </c>
@@ -6042,7 +5743,7 @@
       <c r="N83"/>
       <c r="O83"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>54</v>
       </c>
@@ -6083,7 +5784,7 @@
       <c r="N84"/>
       <c r="O84"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>50</v>
       </c>
@@ -6124,7 +5825,7 @@
       <c r="N85"/>
       <c r="O85"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>54</v>
       </c>
@@ -6165,7 +5866,7 @@
       <c r="N86"/>
       <c r="O86"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>50</v>
       </c>
@@ -6206,7 +5907,7 @@
       <c r="N87"/>
       <c r="O87"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>54</v>
       </c>
@@ -6247,7 +5948,7 @@
       <c r="N88"/>
       <c r="O88"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>50</v>
       </c>
@@ -6288,7 +5989,7 @@
       <c r="N89"/>
       <c r="O89"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>54</v>
       </c>
@@ -6329,7 +6030,7 @@
       <c r="N90"/>
       <c r="O90"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>50</v>
       </c>
@@ -6370,7 +6071,7 @@
       <c r="N91"/>
       <c r="O91"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>54</v>
       </c>
@@ -6411,7 +6112,7 @@
       <c r="N92"/>
       <c r="O92"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>50</v>
       </c>
@@ -6452,7 +6153,7 @@
       <c r="N93"/>
       <c r="O93"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>39</v>
       </c>
@@ -6493,7 +6194,7 @@
       <c r="N94"/>
       <c r="O94"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>42</v>
       </c>
@@ -6534,7 +6235,7 @@
       <c r="N95"/>
       <c r="O95"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>45</v>
       </c>
@@ -6575,7 +6276,7 @@
       <c r="N96"/>
       <c r="O96"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>45</v>
       </c>
@@ -6616,7 +6317,7 @@
       <c r="N97"/>
       <c r="O97"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>54</v>
       </c>
@@ -6657,7 +6358,7 @@
       <c r="N98"/>
       <c r="O98"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>54</v>
       </c>
@@ -6743,7 +6444,7 @@
       </c>
       <c r="O100"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>115</v>
       </c>
@@ -6833,7 +6534,7 @@
       </c>
       <c r="O102"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -6878,7 +6579,7 @@
       </c>
       <c r="O103"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>118</v>
       </c>
@@ -6920,10 +6621,10 @@
         <v>117</v>
       </c>
       <c r="O104" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>121</v>
       </c>
@@ -6965,7 +6666,7 @@
         <v>13</v>
       </c>
       <c r="O105" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
@@ -7010,7 +6711,7 @@
         <v>117</v>
       </c>
       <c r="O106" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
@@ -7024,7 +6725,7 @@
         <v>112</v>
       </c>
       <c r="D107" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E107" t="s">
         <v>19</v>
@@ -7055,10 +6756,10 @@
         <v>13</v>
       </c>
       <c r="O107" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>118</v>
       </c>
@@ -7081,7 +6782,7 @@
         <v>107</v>
       </c>
       <c r="H108" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I108" t="s">
         <v>88</v>
@@ -7100,7 +6801,7 @@
         <v>117</v>
       </c>
       <c r="O108" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
@@ -7126,7 +6827,7 @@
         <v>107</v>
       </c>
       <c r="H109" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I109" t="s">
         <v>88</v>
@@ -7145,10 +6846,10 @@
         <v>117</v>
       </c>
       <c r="O109" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>121</v>
       </c>
@@ -7171,7 +6872,7 @@
         <v>107</v>
       </c>
       <c r="H110" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I110" t="s">
         <v>88</v>
@@ -7190,7 +6891,7 @@
         <v>13</v>
       </c>
       <c r="O110" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
@@ -7204,7 +6905,7 @@
         <v>112</v>
       </c>
       <c r="D111" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
@@ -7216,7 +6917,7 @@
         <v>107</v>
       </c>
       <c r="H111" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I111" t="s">
         <v>88</v>
@@ -7235,10 +6936,10 @@
         <v>13</v>
       </c>
       <c r="O111" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>118</v>
       </c>
@@ -7276,14 +6977,14 @@
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N112" t="s">
         <v>117</v>
       </c>
       <c r="O112"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>121</v>
       </c>
@@ -7312,7 +7013,7 @@
         <v>108</v>
       </c>
       <c r="J113" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K113" t="s">
         <v>110</v>
@@ -7321,14 +7022,14 @@
         <v>3</v>
       </c>
       <c r="M113" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N113" t="s">
         <v>13</v>
       </c>
       <c r="O113"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -7366,14 +7067,14 @@
         <v>6</v>
       </c>
       <c r="M114" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N114" t="s">
         <v>13</v>
       </c>
       <c r="O114"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>14</v>
       </c>
@@ -7411,14 +7112,14 @@
         <v>6</v>
       </c>
       <c r="M115" t="s">
+        <v>129</v>
+      </c>
+      <c r="N115" t="s">
         <v>130</v>
       </c>
-      <c r="N115" t="s">
-        <v>131</v>
-      </c>
       <c r="O115"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>5</v>
       </c>
@@ -7456,14 +7157,14 @@
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N116" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O116"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -7486,7 +7187,7 @@
         <v>107</v>
       </c>
       <c r="H117" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I117" t="s">
         <v>88</v>
@@ -7501,14 +7202,14 @@
         <v>6</v>
       </c>
       <c r="M117" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N117" t="s">
         <v>13</v>
       </c>
       <c r="O117"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>14</v>
       </c>
@@ -7531,7 +7232,7 @@
         <v>107</v>
       </c>
       <c r="H118" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I118" t="s">
         <v>88</v>
@@ -7546,14 +7247,14 @@
         <v>6</v>
       </c>
       <c r="M118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N118" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O118"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -7576,7 +7277,7 @@
         <v>107</v>
       </c>
       <c r="H119" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I119" t="s">
         <v>88</v>
@@ -7591,16 +7292,16 @@
         <v>0</v>
       </c>
       <c r="M119" t="s">
+        <v>133</v>
+      </c>
+      <c r="N119" t="s">
+        <v>131</v>
+      </c>
+      <c r="O119"/>
+    </row>
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>134</v>
-      </c>
-      <c r="N119" t="s">
-        <v>132</v>
-      </c>
-      <c r="O119"/>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>135</v>
       </c>
       <c r="B120">
         <v>40707</v>
@@ -7609,7 +7310,7 @@
         <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E120" t="s">
         <v>19</v>
@@ -7621,7 +7322,7 @@
         <v>107</v>
       </c>
       <c r="H120" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I120" t="s">
         <v>84</v>
@@ -7636,16 +7337,16 @@
         <v>6</v>
       </c>
       <c r="M120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N120" t="s">
         <v>13</v>
       </c>
       <c r="O120"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B121">
         <v>40708</v>
@@ -7654,7 +7355,7 @@
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
@@ -7666,7 +7367,7 @@
         <v>107</v>
       </c>
       <c r="H121" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I121" t="s">
         <v>84</v>
@@ -7681,16 +7382,16 @@
         <v>6</v>
       </c>
       <c r="M121" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N121" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O121"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B122">
         <v>40709</v>
@@ -7699,7 +7400,7 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E122" t="s">
         <v>19</v>
@@ -7711,7 +7412,7 @@
         <v>107</v>
       </c>
       <c r="H122" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I122" t="s">
         <v>84</v>
@@ -7726,16 +7427,16 @@
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N122" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O122"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B123">
         <v>40710</v>
@@ -7744,7 +7445,7 @@
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -7771,16 +7472,16 @@
         <v>6</v>
       </c>
       <c r="M123" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N123" t="s">
         <v>13</v>
       </c>
       <c r="O123"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B124">
         <v>40711</v>
@@ -7789,7 +7490,7 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -7816,16 +7517,16 @@
         <v>6</v>
       </c>
       <c r="M124" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N124" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O124"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B125">
         <v>40712</v>
@@ -7834,7 +7535,7 @@
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -7861,16 +7562,16 @@
         <v>0</v>
       </c>
       <c r="M125" t="s">
+        <v>141</v>
+      </c>
+      <c r="N125" t="s">
+        <v>131</v>
+      </c>
+      <c r="O125"/>
+    </row>
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>142</v>
-      </c>
-      <c r="N125" t="s">
-        <v>132</v>
-      </c>
-      <c r="O125"/>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>143</v>
       </c>
       <c r="B126">
         <v>40713</v>
@@ -7879,7 +7580,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E126" t="s">
         <v>19</v>
@@ -7891,7 +7592,7 @@
         <v>107</v>
       </c>
       <c r="H126" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I126" t="s">
         <v>84</v>
@@ -7906,16 +7607,16 @@
         <v>6</v>
       </c>
       <c r="M126" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N126" t="s">
         <v>13</v>
       </c>
       <c r="O126"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B127">
         <v>40714</v>
@@ -7924,7 +7625,7 @@
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E127" t="s">
         <v>19</v>
@@ -7936,7 +7637,7 @@
         <v>107</v>
       </c>
       <c r="H127" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I127" t="s">
         <v>84</v>
@@ -7951,16 +7652,16 @@
         <v>6</v>
       </c>
       <c r="M127" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O127"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B128">
         <v>40715</v>
@@ -7969,7 +7670,7 @@
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E128" t="s">
         <v>19</v>
@@ -7981,7 +7682,7 @@
         <v>107</v>
       </c>
       <c r="H128" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I128" t="s">
         <v>84</v>
@@ -7996,16 +7697,16 @@
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O128"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B129">
         <v>40716</v>
@@ -8014,7 +7715,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -8041,16 +7742,16 @@
         <v>6</v>
       </c>
       <c r="M129" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N129" t="s">
         <v>13</v>
       </c>
       <c r="O129"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B130">
         <v>40717</v>
@@ -8059,7 +7760,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -8086,16 +7787,16 @@
         <v>6</v>
       </c>
       <c r="M130" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N130" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O130"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B131">
         <v>40718</v>
@@ -8104,7 +7805,7 @@
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -8131,16 +7832,16 @@
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N131" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O131"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B132">
         <v>40719</v>
@@ -8149,7 +7850,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -8176,16 +7877,16 @@
         <v>6</v>
       </c>
       <c r="M132" t="s">
+        <v>158</v>
+      </c>
+      <c r="N132" t="s">
+        <v>130</v>
+      </c>
+      <c r="O132"/>
+    </row>
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>159</v>
-      </c>
-      <c r="N132" t="s">
-        <v>131</v>
-      </c>
-      <c r="O132"/>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>160</v>
       </c>
       <c r="B133">
         <v>40720</v>
@@ -8194,7 +7895,7 @@
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -8221,14 +7922,14 @@
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N133" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O133"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>21</v>
       </c>
@@ -8251,7 +7952,7 @@
         <v>107</v>
       </c>
       <c r="H134" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I134" t="s">
         <v>88</v>
@@ -8266,14 +7967,14 @@
         <v>6</v>
       </c>
       <c r="M134" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N134" t="s">
         <v>13</v>
       </c>
       <c r="O134"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>23</v>
       </c>
@@ -8296,7 +7997,7 @@
         <v>107</v>
       </c>
       <c r="H135" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I135" t="s">
         <v>88</v>
@@ -8311,14 +8012,14 @@
         <v>6</v>
       </c>
       <c r="M135" t="s">
+        <v>162</v>
+      </c>
+      <c r="N135" t="s">
         <v>163</v>
       </c>
-      <c r="N135" t="s">
-        <v>164</v>
-      </c>
       <c r="O135"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>16</v>
       </c>
@@ -8341,7 +8042,7 @@
         <v>107</v>
       </c>
       <c r="H136" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I136" t="s">
         <v>88</v>
@@ -8356,16 +8057,16 @@
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N136" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O136"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B137">
         <v>40728</v>
@@ -8374,7 +8075,7 @@
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E137" t="s">
         <v>19</v>
@@ -8401,16 +8102,16 @@
         <v>6</v>
       </c>
       <c r="M137" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N137" t="s">
         <v>13</v>
       </c>
       <c r="O137"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B138">
         <v>40729</v>
@@ -8419,7 +8120,7 @@
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E138" t="s">
         <v>19</v>
@@ -8446,16 +8147,16 @@
         <v>6</v>
       </c>
       <c r="M138" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N138" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O138"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B139">
         <v>40730</v>
@@ -8464,7 +8165,7 @@
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E139" t="s">
         <v>19</v>
@@ -8491,16 +8192,16 @@
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N139" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O139"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B140">
         <v>40731</v>
@@ -8509,7 +8210,7 @@
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E140" t="s">
         <v>19</v>
@@ -8536,16 +8237,16 @@
         <v>6</v>
       </c>
       <c r="M140" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N140" t="s">
         <v>13</v>
       </c>
       <c r="O140"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B141">
         <v>40732</v>
@@ -8554,7 +8255,7 @@
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E141" t="s">
         <v>19</v>
@@ -8581,16 +8282,16 @@
         <v>6</v>
       </c>
       <c r="M141" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N141" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O141"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B142">
         <v>40733</v>
@@ -8599,7 +8300,7 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E142" t="s">
         <v>19</v>
@@ -8626,16 +8327,16 @@
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N142" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O142"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B143">
         <v>40734</v>
@@ -8644,7 +8345,7 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E143" t="s">
         <v>19</v>
@@ -8656,7 +8357,7 @@
         <v>107</v>
       </c>
       <c r="H143" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I143" t="s">
         <v>84</v>
@@ -8671,16 +8372,16 @@
         <v>6</v>
       </c>
       <c r="M143" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N143" t="s">
         <v>13</v>
       </c>
       <c r="O143"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B144">
         <v>40735</v>
@@ -8689,7 +8390,7 @@
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E144" t="s">
         <v>19</v>
@@ -8701,7 +8402,7 @@
         <v>107</v>
       </c>
       <c r="H144" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I144" t="s">
         <v>84</v>
@@ -8716,16 +8417,16 @@
         <v>6</v>
       </c>
       <c r="M144" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N144" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O144"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B145">
         <v>40736</v>
@@ -8734,7 +8435,7 @@
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E145" t="s">
         <v>19</v>
@@ -8746,7 +8447,7 @@
         <v>107</v>
       </c>
       <c r="H145" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I145" t="s">
         <v>84</v>
@@ -8761,16 +8462,16 @@
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N145" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O145"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B146">
         <v>40737</v>
@@ -8779,7 +8480,7 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E146" t="s">
         <v>19</v>
@@ -8806,16 +8507,16 @@
         <v>6</v>
       </c>
       <c r="M146" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N146" t="s">
         <v>13</v>
       </c>
       <c r="O146"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B147">
         <v>40738</v>
@@ -8824,7 +8525,7 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E147" t="s">
         <v>19</v>
@@ -8851,16 +8552,16 @@
         <v>6</v>
       </c>
       <c r="M147" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N147" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O147"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B148">
         <v>40739</v>
@@ -8869,7 +8570,7 @@
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E148" t="s">
         <v>19</v>
@@ -8896,14 +8597,14 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N148" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O148"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>29</v>
       </c>
@@ -8941,14 +8642,14 @@
         <v>6</v>
       </c>
       <c r="M149" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N149" t="s">
         <v>13</v>
       </c>
       <c r="O149"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>31</v>
       </c>
@@ -8986,14 +8687,14 @@
         <v>6</v>
       </c>
       <c r="M150" t="s">
+        <v>192</v>
+      </c>
+      <c r="N150" t="s">
         <v>193</v>
       </c>
-      <c r="N150" t="s">
-        <v>194</v>
-      </c>
       <c r="O150"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>25</v>
       </c>
@@ -9031,14 +8732,14 @@
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N151" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O151"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>35</v>
       </c>
@@ -9076,14 +8777,14 @@
         <v>6</v>
       </c>
       <c r="M152" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N152" t="s">
         <v>13</v>
       </c>
       <c r="O152"/>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>37</v>
       </c>
@@ -9121,14 +8822,14 @@
         <v>6</v>
       </c>
       <c r="M153" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N153" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O153"/>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>33</v>
       </c>
@@ -9166,16 +8867,16 @@
         <v>0</v>
       </c>
       <c r="M154" t="s">
+        <v>194</v>
+      </c>
+      <c r="N154" t="s">
+        <v>131</v>
+      </c>
+      <c r="O154"/>
+    </row>
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>195</v>
-      </c>
-      <c r="N154" t="s">
-        <v>132</v>
-      </c>
-      <c r="O154"/>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>196</v>
       </c>
       <c r="B155">
         <v>40749</v>
@@ -9184,7 +8885,7 @@
         <v>26</v>
       </c>
       <c r="D155" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E155" t="s">
         <v>19</v>
@@ -9196,7 +8897,7 @@
         <v>107</v>
       </c>
       <c r="H155" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I155" t="s">
         <v>88</v>
@@ -9211,16 +8912,16 @@
         <v>6</v>
       </c>
       <c r="M155" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N155" t="s">
         <v>13</v>
       </c>
       <c r="O155"/>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B156">
         <v>40750</v>
@@ -9229,7 +8930,7 @@
         <v>26</v>
       </c>
       <c r="D156" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E156" t="s">
         <v>19</v>
@@ -9241,7 +8942,7 @@
         <v>107</v>
       </c>
       <c r="H156" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I156" t="s">
         <v>88</v>
@@ -9256,16 +8957,16 @@
         <v>6</v>
       </c>
       <c r="M156" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N156" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O156"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B157">
         <v>40751</v>
@@ -9274,7 +8975,7 @@
         <v>26</v>
       </c>
       <c r="D157" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E157" t="s">
         <v>19</v>
@@ -9286,7 +8987,7 @@
         <v>107</v>
       </c>
       <c r="H157" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I157" t="s">
         <v>88</v>
@@ -9301,16 +9002,16 @@
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N157" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O157"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B158">
         <v>40752</v>
@@ -9319,7 +9020,7 @@
         <v>26</v>
       </c>
       <c r="D158" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E158" t="s">
         <v>19</v>
@@ -9331,7 +9032,7 @@
         <v>107</v>
       </c>
       <c r="H158" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I158" t="s">
         <v>84</v>
@@ -9346,16 +9047,16 @@
         <v>6</v>
       </c>
       <c r="M158" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N158" t="s">
         <v>13</v>
       </c>
       <c r="O158"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B159">
         <v>40753</v>
@@ -9364,7 +9065,7 @@
         <v>26</v>
       </c>
       <c r="D159" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E159" t="s">
         <v>19</v>
@@ -9376,7 +9077,7 @@
         <v>107</v>
       </c>
       <c r="H159" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I159" t="s">
         <v>84</v>
@@ -9391,16 +9092,16 @@
         <v>6</v>
       </c>
       <c r="M159" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N159" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O159"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B160">
         <v>40754</v>
@@ -9409,7 +9110,7 @@
         <v>26</v>
       </c>
       <c r="D160" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E160" t="s">
         <v>19</v>
@@ -9421,7 +9122,7 @@
         <v>107</v>
       </c>
       <c r="H160" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I160" t="s">
         <v>84</v>
@@ -9436,16 +9137,16 @@
         <v>0</v>
       </c>
       <c r="M160" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N160" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O160"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B161">
         <v>40755</v>
@@ -9454,7 +9155,7 @@
         <v>26</v>
       </c>
       <c r="D161" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E161" t="s">
         <v>19</v>
@@ -9466,7 +9167,7 @@
         <v>107</v>
       </c>
       <c r="H161" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I161" t="s">
         <v>88</v>
@@ -9481,16 +9182,16 @@
         <v>6</v>
       </c>
       <c r="M161" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N161" t="s">
         <v>13</v>
       </c>
       <c r="O161"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B162">
         <v>40756</v>
@@ -9499,7 +9200,7 @@
         <v>26</v>
       </c>
       <c r="D162" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E162" t="s">
         <v>19</v>
@@ -9511,7 +9212,7 @@
         <v>107</v>
       </c>
       <c r="H162" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I162" t="s">
         <v>88</v>
@@ -9526,16 +9227,16 @@
         <v>6</v>
       </c>
       <c r="M162" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N162" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O162"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B163">
         <v>40757</v>
@@ -9544,7 +9245,7 @@
         <v>26</v>
       </c>
       <c r="D163" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E163" t="s">
         <v>19</v>
@@ -9556,7 +9257,7 @@
         <v>107</v>
       </c>
       <c r="H163" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I163" t="s">
         <v>88</v>
@@ -9571,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N163" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O163"/>
     </row>
@@ -9688,41 +9389,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{3A4CF648-6AED-40f4-86FF-DC5316D8AED3}">
-      <x14:slicerList xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicer r:id="rId3"/>
-      </x14:slicerList>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -9923,10 +9596,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9943,20 +9647,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/202660_UAX_OfertaLenguas.xlsx
+++ b/202660_UAX_OfertaLenguas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202660/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{2F2356BF-5FED-4956-B6D5-A4DB07EC43D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9403812-D451-497E-BF33-B33AB4B06439}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{2F2356BF-5FED-4956-B6D5-A4DB07EC43D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2642A279-443F-4609-925F-194D51F9BFBE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
@@ -380,27 +380,18 @@
     <t>Inglés certificación</t>
   </si>
   <si>
-    <t>English academic purposes</t>
-  </si>
-  <si>
     <t>Gidi Marti Daniel Jacobo</t>
   </si>
   <si>
     <t>IDI4432</t>
   </si>
   <si>
-    <t>Expresió oral escrit ingl acad</t>
-  </si>
-  <si>
     <t>Plan 2020</t>
   </si>
   <si>
     <t>TCUG0430</t>
   </si>
   <si>
-    <t>Taller First Certificate</t>
-  </si>
-  <si>
     <t>1,3,5</t>
   </si>
   <si>
@@ -410,9 +401,6 @@
     <t>TCUG0432</t>
   </si>
   <si>
-    <t>English Grammar</t>
-  </si>
-  <si>
     <t>2,4</t>
   </si>
   <si>
@@ -695,28 +683,40 @@
     <t>5°nivel de italiano</t>
   </si>
   <si>
-    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40693.</t>
-  </si>
-  <si>
-    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40694.</t>
-  </si>
-  <si>
-    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40691.</t>
-  </si>
-  <si>
-    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40692.</t>
-  </si>
-  <si>
-    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40696.</t>
-  </si>
-  <si>
-    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40695.</t>
-  </si>
-  <si>
-    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40698.</t>
-  </si>
-  <si>
-    <t>Este curso debe inscribirse obligatoriamente junto con el NRC 40697.</t>
+    <t>C1 English academic purposes</t>
+  </si>
+  <si>
+    <t>C1 Expresió oral escrit ingl acad</t>
+  </si>
+  <si>
+    <t>B2 English Grammar</t>
+  </si>
+  <si>
+    <t>B2 Taller First Certificate</t>
+  </si>
+  <si>
+    <t>este curso debe inscribirse obligatoriamente junto con el NRC 40691.</t>
+  </si>
+  <si>
+    <t>este curso debe inscribirse obligatoriamente junto con el NRC 40692.</t>
+  </si>
+  <si>
+    <t>este curso debe inscribirse obligatoriamente junto con el NRC 40695.</t>
+  </si>
+  <si>
+    <t>este curso debe inscribirse obligatoriamente junto con el NRC 40697.</t>
+  </si>
+  <si>
+    <t>este curso debe inscribirse obligatoriamente junto con el NRC 40693.</t>
+  </si>
+  <si>
+    <t>este curso debe inscribirse obligatoriamente junto con el NRC 40694.</t>
+  </si>
+  <si>
+    <t>este curso debe inscribirse obligatoriamente junto con el NRC 40696.</t>
+  </si>
+  <si>
+    <t>este curso debe inscribirse obligatoriamente junto con el NRC 40698.</t>
   </si>
 </sst>
 </file>
@@ -1963,18 +1963,21 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:O163" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A1:O163" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}">
-    <filterColumn colId="3">
+    <filterColumn colId="2">
       <filters>
-        <filter val="English academic purposes"/>
-        <filter val="English Grammar"/>
+        <filter val="Inglés certificación"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O163">
-    <sortCondition ref="B1:B163"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A100:O113">
+    <sortCondition ref="D1:D163"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="ClaveBanner" dataDxfId="14"/>
@@ -2319,12 +2322,12 @@
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="7.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" style="6" customWidth="1"/>
     <col min="10" max="11" width="8.42578125" style="6" customWidth="1"/>
     <col min="12" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
@@ -6410,7 +6413,7 @@
         <v>112</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>214</v>
       </c>
       <c r="E100" t="s">
         <v>19</v>
@@ -6422,7 +6425,7 @@
         <v>107</v>
       </c>
       <c r="H100" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I100" t="s">
         <v>84</v>
@@ -6444,18 +6447,18 @@
       </c>
       <c r="O100"/>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B101">
-        <v>40688</v>
+        <v>40689</v>
       </c>
       <c r="C101" t="s">
         <v>112</v>
       </c>
       <c r="D101" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
@@ -6467,13 +6470,13 @@
         <v>107</v>
       </c>
       <c r="H101" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="I101" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J101" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K101" t="s">
         <v>73</v>
@@ -6482,25 +6485,25 @@
         <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N101" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="O101"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B102">
-        <v>40689</v>
+        <v>40693</v>
       </c>
       <c r="C102" t="s">
         <v>112</v>
       </c>
       <c r="D102" t="s">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="E102" t="s">
         <v>19</v>
@@ -6515,37 +6518,37 @@
         <v>60</v>
       </c>
       <c r="I102" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J102" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K102" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="L102">
-        <v>6</v>
-      </c>
-      <c r="M102" t="s">
-        <v>79</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M102"/>
       <c r="N102" t="s">
-        <v>13</v>
-      </c>
-      <c r="O102"/>
-    </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="O102" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B103">
-        <v>40690</v>
+        <v>40694</v>
       </c>
       <c r="C103" t="s">
         <v>112</v>
       </c>
       <c r="D103" t="s">
-        <v>116</v>
+        <v>216</v>
       </c>
       <c r="E103" t="s">
         <v>19</v>
@@ -6560,37 +6563,37 @@
         <v>60</v>
       </c>
       <c r="I103" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J103" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K103" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="L103">
-        <v>6</v>
-      </c>
-      <c r="M103" t="s">
-        <v>79</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M103"/>
       <c r="N103" t="s">
-        <v>117</v>
-      </c>
-      <c r="O103"/>
-    </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="O103" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B104">
-        <v>40691</v>
+        <v>40696</v>
       </c>
       <c r="C104" t="s">
         <v>112</v>
       </c>
       <c r="D104" t="s">
-        <v>119</v>
+        <v>216</v>
       </c>
       <c r="E104" t="s">
         <v>19</v>
@@ -6602,13 +6605,13 @@
         <v>107</v>
       </c>
       <c r="H104" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="I104" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J104" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K104" t="s">
         <v>120</v>
@@ -6618,24 +6621,24 @@
       </c>
       <c r="M104"/>
       <c r="N104" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O104" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>121</v>
       </c>
       <c r="B105">
-        <v>40692</v>
+        <v>40698</v>
       </c>
       <c r="C105" t="s">
         <v>112</v>
       </c>
       <c r="D105" t="s">
-        <v>119</v>
+        <v>216</v>
       </c>
       <c r="E105" t="s">
         <v>19</v>
@@ -6647,13 +6650,13 @@
         <v>107</v>
       </c>
       <c r="H105" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="I105" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J105" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K105" t="s">
         <v>120</v>
@@ -6666,21 +6669,21 @@
         <v>13</v>
       </c>
       <c r="O105" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B106">
-        <v>40693</v>
+        <v>40688</v>
       </c>
       <c r="C106" t="s">
         <v>112</v>
       </c>
       <c r="D106" t="s">
-        <v>123</v>
+        <v>215</v>
       </c>
       <c r="E106" t="s">
         <v>19</v>
@@ -6692,7 +6695,7 @@
         <v>107</v>
       </c>
       <c r="H106" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="I106" t="s">
         <v>84</v>
@@ -6701,31 +6704,31 @@
         <v>85</v>
       </c>
       <c r="K106" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="L106">
-        <v>3</v>
-      </c>
-      <c r="M106"/>
+        <v>6</v>
+      </c>
+      <c r="M106" t="s">
+        <v>78</v>
+      </c>
       <c r="N106" t="s">
-        <v>117</v>
-      </c>
-      <c r="O106" t="s">
-        <v>220</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O106"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B107">
-        <v>40694</v>
+        <v>40690</v>
       </c>
       <c r="C107" t="s">
         <v>112</v>
       </c>
       <c r="D107" t="s">
-        <v>123</v>
+        <v>215</v>
       </c>
       <c r="E107" t="s">
         <v>19</v>
@@ -6740,37 +6743,37 @@
         <v>60</v>
       </c>
       <c r="I107" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J107" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K107" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="L107">
-        <v>3</v>
-      </c>
-      <c r="M107"/>
+        <v>6</v>
+      </c>
+      <c r="M107" t="s">
+        <v>79</v>
+      </c>
       <c r="N107" t="s">
-        <v>13</v>
-      </c>
-      <c r="O107" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="O107"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B108">
-        <v>40695</v>
+        <v>40691</v>
       </c>
       <c r="C108" t="s">
         <v>112</v>
       </c>
       <c r="D108" t="s">
-        <v>119</v>
+        <v>217</v>
       </c>
       <c r="E108" t="s">
         <v>19</v>
@@ -6782,23 +6785,23 @@
         <v>107</v>
       </c>
       <c r="H108" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="I108" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J108" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K108" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L108">
         <v>3</v>
       </c>
       <c r="M108"/>
       <c r="N108" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O108" t="s">
         <v>222</v>
@@ -6806,16 +6809,16 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B109">
-        <v>40696</v>
+        <v>40692</v>
       </c>
       <c r="C109" t="s">
         <v>112</v>
       </c>
       <c r="D109" t="s">
-        <v>123</v>
+        <v>217</v>
       </c>
       <c r="E109" t="s">
         <v>19</v>
@@ -6827,40 +6830,40 @@
         <v>107</v>
       </c>
       <c r="H109" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="I109" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J109" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K109" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="L109">
         <v>3</v>
       </c>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="O109" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B110">
-        <v>40697</v>
+        <v>40695</v>
       </c>
       <c r="C110" t="s">
         <v>112</v>
       </c>
       <c r="D110" t="s">
-        <v>119</v>
+        <v>217</v>
       </c>
       <c r="E110" t="s">
         <v>19</v>
@@ -6872,7 +6875,7 @@
         <v>107</v>
       </c>
       <c r="H110" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I110" t="s">
         <v>88</v>
@@ -6881,14 +6884,14 @@
         <v>89</v>
       </c>
       <c r="K110" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L110">
         <v>3</v>
       </c>
       <c r="M110"/>
       <c r="N110" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="O110" t="s">
         <v>224</v>
@@ -6896,16 +6899,16 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B111">
-        <v>40698</v>
+        <v>40697</v>
       </c>
       <c r="C111" t="s">
         <v>112</v>
       </c>
       <c r="D111" t="s">
-        <v>123</v>
+        <v>217</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
@@ -6917,7 +6920,7 @@
         <v>107</v>
       </c>
       <c r="H111" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I111" t="s">
         <v>88</v>
@@ -6926,7 +6929,7 @@
         <v>89</v>
       </c>
       <c r="K111" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="L111">
         <v>3</v>
@@ -6939,9 +6942,9 @@
         <v>225</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B112">
         <v>40699</v>
@@ -6950,7 +6953,7 @@
         <v>112</v>
       </c>
       <c r="D112" t="s">
-        <v>119</v>
+        <v>217</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -6977,16 +6980,16 @@
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N112" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O112"/>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B113">
         <v>40700</v>
@@ -6995,7 +6998,7 @@
         <v>112</v>
       </c>
       <c r="D113" t="s">
-        <v>119</v>
+        <v>217</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -7013,7 +7016,7 @@
         <v>108</v>
       </c>
       <c r="J113" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K113" t="s">
         <v>110</v>
@@ -7022,7 +7025,7 @@
         <v>3</v>
       </c>
       <c r="M113" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N113" t="s">
         <v>13</v>
@@ -7067,7 +7070,7 @@
         <v>6</v>
       </c>
       <c r="M114" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N114" t="s">
         <v>13</v>
@@ -7112,10 +7115,10 @@
         <v>6</v>
       </c>
       <c r="M115" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N115" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O115"/>
     </row>
@@ -7157,10 +7160,10 @@
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N116" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O116"/>
     </row>
@@ -7187,7 +7190,7 @@
         <v>107</v>
       </c>
       <c r="H117" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I117" t="s">
         <v>88</v>
@@ -7202,7 +7205,7 @@
         <v>6</v>
       </c>
       <c r="M117" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N117" t="s">
         <v>13</v>
@@ -7232,7 +7235,7 @@
         <v>107</v>
       </c>
       <c r="H118" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I118" t="s">
         <v>88</v>
@@ -7247,10 +7250,10 @@
         <v>6</v>
       </c>
       <c r="M118" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N118" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O118"/>
     </row>
@@ -7277,7 +7280,7 @@
         <v>107</v>
       </c>
       <c r="H119" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I119" t="s">
         <v>88</v>
@@ -7292,16 +7295,16 @@
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N119" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O119"/>
     </row>
     <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B120">
         <v>40707</v>
@@ -7310,7 +7313,7 @@
         <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E120" t="s">
         <v>19</v>
@@ -7322,7 +7325,7 @@
         <v>107</v>
       </c>
       <c r="H120" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I120" t="s">
         <v>84</v>
@@ -7337,7 +7340,7 @@
         <v>6</v>
       </c>
       <c r="M120" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N120" t="s">
         <v>13</v>
@@ -7346,7 +7349,7 @@
     </row>
     <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B121">
         <v>40708</v>
@@ -7355,7 +7358,7 @@
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
@@ -7367,7 +7370,7 @@
         <v>107</v>
       </c>
       <c r="H121" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I121" t="s">
         <v>84</v>
@@ -7382,16 +7385,16 @@
         <v>6</v>
       </c>
       <c r="M121" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N121" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O121"/>
     </row>
     <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B122">
         <v>40709</v>
@@ -7400,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E122" t="s">
         <v>19</v>
@@ -7412,7 +7415,7 @@
         <v>107</v>
       </c>
       <c r="H122" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I122" t="s">
         <v>84</v>
@@ -7427,16 +7430,16 @@
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N122" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O122"/>
     </row>
     <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B123">
         <v>40710</v>
@@ -7445,7 +7448,7 @@
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -7472,7 +7475,7 @@
         <v>6</v>
       </c>
       <c r="M123" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N123" t="s">
         <v>13</v>
@@ -7481,7 +7484,7 @@
     </row>
     <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B124">
         <v>40711</v>
@@ -7490,7 +7493,7 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -7517,16 +7520,16 @@
         <v>6</v>
       </c>
       <c r="M124" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N124" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O124"/>
     </row>
     <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B125">
         <v>40712</v>
@@ -7535,7 +7538,7 @@
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -7562,16 +7565,16 @@
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N125" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O125"/>
     </row>
     <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B126">
         <v>40713</v>
@@ -7580,7 +7583,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E126" t="s">
         <v>19</v>
@@ -7592,7 +7595,7 @@
         <v>107</v>
       </c>
       <c r="H126" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I126" t="s">
         <v>84</v>
@@ -7607,7 +7610,7 @@
         <v>6</v>
       </c>
       <c r="M126" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N126" t="s">
         <v>13</v>
@@ -7616,7 +7619,7 @@
     </row>
     <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B127">
         <v>40714</v>
@@ -7625,7 +7628,7 @@
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E127" t="s">
         <v>19</v>
@@ -7637,7 +7640,7 @@
         <v>107</v>
       </c>
       <c r="H127" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I127" t="s">
         <v>84</v>
@@ -7652,16 +7655,16 @@
         <v>6</v>
       </c>
       <c r="M127" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N127" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O127"/>
     </row>
     <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B128">
         <v>40715</v>
@@ -7670,7 +7673,7 @@
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E128" t="s">
         <v>19</v>
@@ -7682,7 +7685,7 @@
         <v>107</v>
       </c>
       <c r="H128" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I128" t="s">
         <v>84</v>
@@ -7697,16 +7700,16 @@
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N128" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O128"/>
     </row>
     <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B129">
         <v>40716</v>
@@ -7715,7 +7718,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -7742,7 +7745,7 @@
         <v>6</v>
       </c>
       <c r="M129" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N129" t="s">
         <v>13</v>
@@ -7751,7 +7754,7 @@
     </row>
     <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B130">
         <v>40717</v>
@@ -7760,7 +7763,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -7787,16 +7790,16 @@
         <v>6</v>
       </c>
       <c r="M130" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N130" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O130"/>
     </row>
     <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B131">
         <v>40718</v>
@@ -7805,7 +7808,7 @@
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -7832,16 +7835,16 @@
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N131" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O131"/>
     </row>
     <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B132">
         <v>40719</v>
@@ -7850,7 +7853,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -7877,16 +7880,16 @@
         <v>6</v>
       </c>
       <c r="M132" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N132" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O132"/>
     </row>
     <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B133">
         <v>40720</v>
@@ -7895,7 +7898,7 @@
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -7922,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N133" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O133"/>
     </row>
@@ -7952,7 +7955,7 @@
         <v>107</v>
       </c>
       <c r="H134" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I134" t="s">
         <v>88</v>
@@ -7967,7 +7970,7 @@
         <v>6</v>
       </c>
       <c r="M134" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N134" t="s">
         <v>13</v>
@@ -7997,7 +8000,7 @@
         <v>107</v>
       </c>
       <c r="H135" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I135" t="s">
         <v>88</v>
@@ -8012,10 +8015,10 @@
         <v>6</v>
       </c>
       <c r="M135" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N135" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O135"/>
     </row>
@@ -8042,7 +8045,7 @@
         <v>107</v>
       </c>
       <c r="H136" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I136" t="s">
         <v>88</v>
@@ -8057,16 +8060,16 @@
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N136" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O136"/>
     </row>
     <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B137">
         <v>40728</v>
@@ -8075,7 +8078,7 @@
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E137" t="s">
         <v>19</v>
@@ -8102,7 +8105,7 @@
         <v>6</v>
       </c>
       <c r="M137" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N137" t="s">
         <v>13</v>
@@ -8111,7 +8114,7 @@
     </row>
     <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B138">
         <v>40729</v>
@@ -8120,7 +8123,7 @@
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E138" t="s">
         <v>19</v>
@@ -8147,16 +8150,16 @@
         <v>6</v>
       </c>
       <c r="M138" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N138" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O138"/>
     </row>
     <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B139">
         <v>40730</v>
@@ -8165,7 +8168,7 @@
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E139" t="s">
         <v>19</v>
@@ -8192,16 +8195,16 @@
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N139" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O139"/>
     </row>
     <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B140">
         <v>40731</v>
@@ -8210,7 +8213,7 @@
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E140" t="s">
         <v>19</v>
@@ -8237,7 +8240,7 @@
         <v>6</v>
       </c>
       <c r="M140" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N140" t="s">
         <v>13</v>
@@ -8246,7 +8249,7 @@
     </row>
     <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B141">
         <v>40732</v>
@@ -8255,7 +8258,7 @@
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E141" t="s">
         <v>19</v>
@@ -8282,16 +8285,16 @@
         <v>6</v>
       </c>
       <c r="M141" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N141" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O141"/>
     </row>
     <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B142">
         <v>40733</v>
@@ -8300,7 +8303,7 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E142" t="s">
         <v>19</v>
@@ -8327,16 +8330,16 @@
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N142" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O142"/>
     </row>
     <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B143">
         <v>40734</v>
@@ -8345,7 +8348,7 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E143" t="s">
         <v>19</v>
@@ -8357,7 +8360,7 @@
         <v>107</v>
       </c>
       <c r="H143" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I143" t="s">
         <v>84</v>
@@ -8372,7 +8375,7 @@
         <v>6</v>
       </c>
       <c r="M143" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N143" t="s">
         <v>13</v>
@@ -8381,7 +8384,7 @@
     </row>
     <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B144">
         <v>40735</v>
@@ -8390,7 +8393,7 @@
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E144" t="s">
         <v>19</v>
@@ -8402,7 +8405,7 @@
         <v>107</v>
       </c>
       <c r="H144" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I144" t="s">
         <v>84</v>
@@ -8417,16 +8420,16 @@
         <v>6</v>
       </c>
       <c r="M144" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N144" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O144"/>
     </row>
     <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B145">
         <v>40736</v>
@@ -8435,7 +8438,7 @@
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E145" t="s">
         <v>19</v>
@@ -8447,7 +8450,7 @@
         <v>107</v>
       </c>
       <c r="H145" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I145" t="s">
         <v>84</v>
@@ -8462,16 +8465,16 @@
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N145" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O145"/>
     </row>
     <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B146">
         <v>40737</v>
@@ -8480,7 +8483,7 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E146" t="s">
         <v>19</v>
@@ -8507,7 +8510,7 @@
         <v>6</v>
       </c>
       <c r="M146" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="N146" t="s">
         <v>13</v>
@@ -8516,7 +8519,7 @@
     </row>
     <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B147">
         <v>40738</v>
@@ -8525,7 +8528,7 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E147" t="s">
         <v>19</v>
@@ -8552,16 +8555,16 @@
         <v>6</v>
       </c>
       <c r="M147" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="N147" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O147"/>
     </row>
     <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B148">
         <v>40739</v>
@@ -8570,7 +8573,7 @@
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E148" t="s">
         <v>19</v>
@@ -8597,10 +8600,10 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="N148" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O148"/>
     </row>
@@ -8642,7 +8645,7 @@
         <v>6</v>
       </c>
       <c r="M149" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="N149" t="s">
         <v>13</v>
@@ -8687,10 +8690,10 @@
         <v>6</v>
       </c>
       <c r="M150" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="N150" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O150"/>
     </row>
@@ -8732,10 +8735,10 @@
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="N151" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O151"/>
     </row>
@@ -8777,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="M152" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="N152" t="s">
         <v>13</v>
@@ -8822,10 +8825,10 @@
         <v>6</v>
       </c>
       <c r="M153" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="N153" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O153"/>
     </row>
@@ -8867,16 +8870,16 @@
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="N154" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O154"/>
     </row>
     <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B155">
         <v>40749</v>
@@ -8885,7 +8888,7 @@
         <v>26</v>
       </c>
       <c r="D155" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E155" t="s">
         <v>19</v>
@@ -8897,7 +8900,7 @@
         <v>107</v>
       </c>
       <c r="H155" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I155" t="s">
         <v>88</v>
@@ -8912,7 +8915,7 @@
         <v>6</v>
       </c>
       <c r="M155" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N155" t="s">
         <v>13</v>
@@ -8921,7 +8924,7 @@
     </row>
     <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B156">
         <v>40750</v>
@@ -8930,7 +8933,7 @@
         <v>26</v>
       </c>
       <c r="D156" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E156" t="s">
         <v>19</v>
@@ -8942,7 +8945,7 @@
         <v>107</v>
       </c>
       <c r="H156" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I156" t="s">
         <v>88</v>
@@ -8957,16 +8960,16 @@
         <v>6</v>
       </c>
       <c r="M156" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N156" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O156"/>
     </row>
     <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B157">
         <v>40751</v>
@@ -8975,7 +8978,7 @@
         <v>26</v>
       </c>
       <c r="D157" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E157" t="s">
         <v>19</v>
@@ -8987,7 +8990,7 @@
         <v>107</v>
       </c>
       <c r="H157" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I157" t="s">
         <v>88</v>
@@ -9002,16 +9005,16 @@
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N157" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O157"/>
     </row>
     <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B158">
         <v>40752</v>
@@ -9020,7 +9023,7 @@
         <v>26</v>
       </c>
       <c r="D158" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E158" t="s">
         <v>19</v>
@@ -9032,7 +9035,7 @@
         <v>107</v>
       </c>
       <c r="H158" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I158" t="s">
         <v>84</v>
@@ -9047,7 +9050,7 @@
         <v>6</v>
       </c>
       <c r="M158" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N158" t="s">
         <v>13</v>
@@ -9056,7 +9059,7 @@
     </row>
     <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B159">
         <v>40753</v>
@@ -9065,7 +9068,7 @@
         <v>26</v>
       </c>
       <c r="D159" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E159" t="s">
         <v>19</v>
@@ -9077,7 +9080,7 @@
         <v>107</v>
       </c>
       <c r="H159" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I159" t="s">
         <v>84</v>
@@ -9092,16 +9095,16 @@
         <v>6</v>
       </c>
       <c r="M159" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N159" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O159"/>
     </row>
     <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B160">
         <v>40754</v>
@@ -9110,7 +9113,7 @@
         <v>26</v>
       </c>
       <c r="D160" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E160" t="s">
         <v>19</v>
@@ -9122,7 +9125,7 @@
         <v>107</v>
       </c>
       <c r="H160" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I160" t="s">
         <v>84</v>
@@ -9137,16 +9140,16 @@
         <v>0</v>
       </c>
       <c r="M160" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N160" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O160"/>
     </row>
     <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B161">
         <v>40755</v>
@@ -9155,7 +9158,7 @@
         <v>26</v>
       </c>
       <c r="D161" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E161" t="s">
         <v>19</v>
@@ -9167,7 +9170,7 @@
         <v>107</v>
       </c>
       <c r="H161" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I161" t="s">
         <v>88</v>
@@ -9182,7 +9185,7 @@
         <v>6</v>
       </c>
       <c r="M161" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="N161" t="s">
         <v>13</v>
@@ -9191,7 +9194,7 @@
     </row>
     <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B162">
         <v>40756</v>
@@ -9200,7 +9203,7 @@
         <v>26</v>
       </c>
       <c r="D162" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E162" t="s">
         <v>19</v>
@@ -9212,7 +9215,7 @@
         <v>107</v>
       </c>
       <c r="H162" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I162" t="s">
         <v>88</v>
@@ -9227,16 +9230,16 @@
         <v>6</v>
       </c>
       <c r="M162" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="N162" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O162"/>
     </row>
     <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B163">
         <v>40757</v>
@@ -9245,7 +9248,7 @@
         <v>26</v>
       </c>
       <c r="D163" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E163" t="s">
         <v>19</v>
@@ -9257,7 +9260,7 @@
         <v>107</v>
       </c>
       <c r="H163" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I163" t="s">
         <v>88</v>
@@ -9272,10 +9275,10 @@
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="N163" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O163"/>
     </row>
@@ -9396,6 +9399,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -9596,27 +9619,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9633,23 +9655,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/202660_UAX_OfertaLenguas.xlsx
+++ b/202660_UAX_OfertaLenguas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202660/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{2F2356BF-5FED-4956-B6D5-A4DB07EC43D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2642A279-443F-4609-925F-194D51F9BFBE}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{2F2356BF-5FED-4956-B6D5-A4DB07EC43D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07D8206E-343F-4479-B530-19679FE1D445}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
+    <workbookView xWindow="28680" yWindow="-10740" windowWidth="16440" windowHeight="28320" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="2" r:id="rId1"/>
@@ -161,42 +161,27 @@
     <t>CLINRIN0A</t>
   </si>
   <si>
-    <t>Propedéutico Elementary A</t>
-  </si>
-  <si>
     <t>Ortiz Romero Jaime Rommel</t>
   </si>
   <si>
     <t>CLINRIN1</t>
   </si>
   <si>
-    <t>Pre Intermediate A</t>
-  </si>
-  <si>
     <t>Rivas López Ricardo</t>
   </si>
   <si>
     <t>CLINRIN3</t>
   </si>
   <si>
-    <t>Intermediate A</t>
-  </si>
-  <si>
     <t>Ladrón de Guevara Coutiño Armando</t>
   </si>
   <si>
     <t>CLINRIN4</t>
   </si>
   <si>
-    <t>Intermediate B</t>
-  </si>
-  <si>
     <t>CLINRING</t>
   </si>
   <si>
-    <t>Upper Intermediate B</t>
-  </si>
-  <si>
     <t>Bustamante Herrera Guillermo</t>
   </si>
   <si>
@@ -206,15 +191,9 @@
     <t>CLINRIN5</t>
   </si>
   <si>
-    <t>Upper Intermediate A</t>
-  </si>
-  <si>
     <t>CLINRIN0B</t>
   </si>
   <si>
-    <t>Propedéutico Elementary B</t>
-  </si>
-  <si>
     <t>Huerta Rodríguez César Samir</t>
   </si>
   <si>
@@ -230,9 +209,6 @@
     <t>CLINRIN2</t>
   </si>
   <si>
-    <t>Pre Intermediate B</t>
-  </si>
-  <si>
     <t>Contreras González Guadalupe</t>
   </si>
   <si>
@@ -717,6 +693,30 @@
   </si>
   <si>
     <t>este curso debe inscribirse obligatoriamente junto con el NRC 40698.</t>
+  </si>
+  <si>
+    <t>3 Intermediate A</t>
+  </si>
+  <si>
+    <t>4 Intermediate B</t>
+  </si>
+  <si>
+    <t>1 Pre Intermediate A</t>
+  </si>
+  <si>
+    <t>2 Pre Intermediate B</t>
+  </si>
+  <si>
+    <t>0A Propedéutico Elementary A</t>
+  </si>
+  <si>
+    <t>0B Propedéutico Elementary B</t>
+  </si>
+  <si>
+    <t>5 Upper Intermediate A</t>
+  </si>
+  <si>
+    <t>6 Upper Intermediate B</t>
   </si>
 </sst>
 </file>
@@ -1972,11 +1972,11 @@
   <autoFilter ref="A1:O163" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}">
     <filterColumn colId="2">
       <filters>
-        <filter val="Inglés certificación"/>
+        <filter val="Inglés requisito"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A100:O113">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O99">
     <sortCondition ref="D1:D163"/>
   </sortState>
   <tableColumns count="15">
@@ -2339,7 +2339,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -2348,54 +2348,54 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B2">
-        <v>40493</v>
+        <v>40563</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -2404,19 +2404,19 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2425,18 +2425,18 @@
       <c r="N2"/>
       <c r="O2"/>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B3">
-        <v>40494</v>
+        <v>40565</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -2445,19 +2445,19 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -2466,18 +2466,18 @@
       <c r="N3"/>
       <c r="O3"/>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B4">
-        <v>40495</v>
+        <v>40567</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -2486,19 +2486,19 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2507,39 +2507,39 @@
       <c r="N4"/>
       <c r="O4"/>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B5">
-        <v>40496</v>
+        <v>40569</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2548,18 +2548,18 @@
       <c r="N5"/>
       <c r="O5"/>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>40501</v>
+        <v>40571</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>218</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -2568,19 +2568,19 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J6" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K6" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2589,39 +2589,39 @@
       <c r="N6"/>
       <c r="O6"/>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B7">
-        <v>40502</v>
+        <v>40573</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J7" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K7" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2630,39 +2630,39 @@
       <c r="N7"/>
       <c r="O7"/>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B8">
-        <v>40503</v>
+        <v>40585</v>
       </c>
       <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" t="s">
         <v>81</v>
       </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J8" t="s">
-        <v>89</v>
-      </c>
       <c r="K8" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2671,39 +2671,39 @@
       <c r="N8"/>
       <c r="O8"/>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B9">
-        <v>40504</v>
+        <v>40587</v>
       </c>
       <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" t="s">
         <v>81</v>
       </c>
-      <c r="D9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" t="s">
-        <v>89</v>
-      </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2712,39 +2712,39 @@
       <c r="N9"/>
       <c r="O9"/>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B10">
-        <v>40505</v>
+        <v>40589</v>
       </c>
       <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" t="s">
         <v>81</v>
       </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" t="s">
-        <v>88</v>
-      </c>
-      <c r="J10" t="s">
-        <v>89</v>
-      </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2753,39 +2753,39 @@
       <c r="N10"/>
       <c r="O10"/>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B11">
-        <v>40506</v>
+        <v>40591</v>
       </c>
       <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" t="s">
         <v>81</v>
       </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" t="s">
-        <v>90</v>
-      </c>
-      <c r="I11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J11" t="s">
-        <v>89</v>
-      </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2794,39 +2794,39 @@
       <c r="N11"/>
       <c r="O11"/>
     </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B12">
-        <v>40513</v>
+        <v>40593</v>
       </c>
       <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" t="s">
-        <v>91</v>
-      </c>
-      <c r="J12" t="s">
-        <v>92</v>
-      </c>
       <c r="K12" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2835,39 +2835,39 @@
       <c r="N12"/>
       <c r="O12"/>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B13">
-        <v>40514</v>
+        <v>40595</v>
       </c>
       <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>218</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" t="s">
         <v>81</v>
       </c>
-      <c r="D13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" t="s">
-        <v>92</v>
-      </c>
       <c r="K13" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2876,18 +2876,18 @@
       <c r="N13"/>
       <c r="O13"/>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14">
-        <v>40517</v>
+        <v>40611</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>218</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -2896,19 +2896,19 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2917,18 +2917,18 @@
       <c r="N14"/>
       <c r="O14"/>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B15">
-        <v>40518</v>
+        <v>40683</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -2937,19 +2937,19 @@
         <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J15" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="K15" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2958,39 +2958,39 @@
       <c r="N15"/>
       <c r="O15"/>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16">
-        <v>40525</v>
+        <v>40684</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>218</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J16" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K16" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2999,18 +2999,18 @@
       <c r="N16"/>
       <c r="O16"/>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B17">
-        <v>40526</v>
+        <v>40564</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
@@ -3019,19 +3019,19 @@
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3040,18 +3040,18 @@
       <c r="N17"/>
       <c r="O17"/>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B18">
-        <v>40527</v>
+        <v>40566</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>219</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -3060,19 +3060,19 @@
         <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J18" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K18" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3081,18 +3081,18 @@
       <c r="N18"/>
       <c r="O18"/>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B19">
-        <v>40528</v>
+        <v>40568</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -3101,19 +3101,19 @@
         <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J19" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K19" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3122,39 +3122,39 @@
       <c r="N19"/>
       <c r="O19"/>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B20">
-        <v>40529</v>
+        <v>40570</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>219</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J20" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3163,18 +3163,18 @@
       <c r="N20"/>
       <c r="O20"/>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B21">
-        <v>40530</v>
+        <v>40572</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -3183,19 +3183,19 @@
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="I21" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K21" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3204,39 +3204,39 @@
       <c r="N21"/>
       <c r="O21"/>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B22">
-        <v>40531</v>
+        <v>40574</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>219</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I22" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3245,39 +3245,39 @@
       <c r="N22"/>
       <c r="O22"/>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B23">
-        <v>40532</v>
+        <v>40586</v>
       </c>
       <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>219</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" t="s">
+        <v>80</v>
+      </c>
+      <c r="J23" t="s">
         <v>81</v>
       </c>
-      <c r="D23" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" t="s">
-        <v>86</v>
-      </c>
-      <c r="H23" t="s">
-        <v>61</v>
-      </c>
-      <c r="I23" t="s">
-        <v>84</v>
-      </c>
-      <c r="J23" t="s">
-        <v>85</v>
-      </c>
       <c r="K23" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3286,39 +3286,39 @@
       <c r="N23"/>
       <c r="O23"/>
     </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B24">
-        <v>40539</v>
+        <v>40588</v>
       </c>
       <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" t="s">
+        <v>80</v>
+      </c>
+      <c r="J24" t="s">
         <v>81</v>
       </c>
-      <c r="D24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" t="s">
-        <v>82</v>
-      </c>
-      <c r="H24" t="s">
-        <v>41</v>
-      </c>
-      <c r="I24" t="s">
-        <v>88</v>
-      </c>
-      <c r="J24" t="s">
-        <v>89</v>
-      </c>
       <c r="K24" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3327,39 +3327,39 @@
       <c r="N24"/>
       <c r="O24"/>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B25">
-        <v>40540</v>
+        <v>40590</v>
       </c>
       <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" t="s">
+        <v>80</v>
+      </c>
+      <c r="J25" t="s">
         <v>81</v>
       </c>
-      <c r="D25" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" t="s">
-        <v>86</v>
-      </c>
-      <c r="H25" t="s">
-        <v>41</v>
-      </c>
-      <c r="I25" t="s">
-        <v>88</v>
-      </c>
-      <c r="J25" t="s">
-        <v>89</v>
-      </c>
       <c r="K25" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3368,18 +3368,18 @@
       <c r="N25"/>
       <c r="O25"/>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B26">
-        <v>40541</v>
+        <v>40592</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>219</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -3388,19 +3388,19 @@
         <v>9</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="I26" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J26" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K26" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3409,39 +3409,39 @@
       <c r="N26"/>
       <c r="O26"/>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B27">
-        <v>40542</v>
+        <v>40594</v>
       </c>
       <c r="C27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" t="s">
+        <v>219</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" t="s">
+        <v>80</v>
+      </c>
+      <c r="J27" t="s">
         <v>81</v>
       </c>
-      <c r="D27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" t="s">
-        <v>86</v>
-      </c>
-      <c r="H27" t="s">
-        <v>98</v>
-      </c>
-      <c r="I27" t="s">
-        <v>88</v>
-      </c>
-      <c r="J27" t="s">
-        <v>89</v>
-      </c>
       <c r="K27" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3450,39 +3450,39 @@
       <c r="N27"/>
       <c r="O27"/>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B28">
-        <v>40543</v>
+        <v>40596</v>
       </c>
       <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" t="s">
+        <v>219</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" t="s">
+        <v>80</v>
+      </c>
+      <c r="J28" t="s">
         <v>81</v>
       </c>
-      <c r="D28" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" t="s">
-        <v>82</v>
-      </c>
-      <c r="H28" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" t="s">
-        <v>88</v>
-      </c>
-      <c r="J28" t="s">
-        <v>89</v>
-      </c>
       <c r="K28" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3491,39 +3491,39 @@
       <c r="N28"/>
       <c r="O28"/>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B29">
-        <v>40544</v>
+        <v>40612</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s">
+        <v>58</v>
+      </c>
+      <c r="I29" t="s">
+        <v>85</v>
+      </c>
+      <c r="J29" t="s">
         <v>86</v>
       </c>
-      <c r="H29" t="s">
-        <v>47</v>
-      </c>
-      <c r="I29" t="s">
-        <v>88</v>
-      </c>
-      <c r="J29" t="s">
-        <v>89</v>
-      </c>
       <c r="K29" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3532,18 +3532,18 @@
       <c r="N29"/>
       <c r="O29"/>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30">
-        <v>40551</v>
+        <v>40525</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>220</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
@@ -3552,19 +3552,19 @@
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="I30" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3573,18 +3573,18 @@
       <c r="N30"/>
       <c r="O30"/>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B31">
-        <v>40552</v>
+        <v>40527</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>220</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
@@ -3593,19 +3593,19 @@
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H31" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="I31" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="J31" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="K31" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3614,39 +3614,39 @@
       <c r="N31"/>
       <c r="O31"/>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32">
+        <v>40529</v>
+      </c>
+      <c r="C32" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" t="s">
         <v>42</v>
       </c>
-      <c r="B32">
-        <v>40555</v>
-      </c>
-      <c r="C32" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" t="s">
-        <v>82</v>
-      </c>
-      <c r="H32" t="s">
-        <v>47</v>
-      </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J32" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -3655,39 +3655,39 @@
       <c r="N32"/>
       <c r="O32"/>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B33">
-        <v>40556</v>
+        <v>40531</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>220</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H33" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J33" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3696,39 +3696,39 @@
       <c r="N33"/>
       <c r="O33"/>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>40563</v>
+        <v>40539</v>
       </c>
       <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
+        <v>220</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H34" t="s">
+        <v>40</v>
+      </c>
+      <c r="I34" t="s">
+        <v>80</v>
+      </c>
+      <c r="J34" t="s">
         <v>81</v>
       </c>
-      <c r="D34" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H34" t="s">
-        <v>100</v>
-      </c>
-      <c r="I34" t="s">
-        <v>96</v>
-      </c>
-      <c r="J34" t="s">
-        <v>97</v>
-      </c>
       <c r="K34" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -3737,39 +3737,39 @@
       <c r="N34"/>
       <c r="O34"/>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B35">
-        <v>40564</v>
+        <v>40541</v>
       </c>
       <c r="C35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" t="s">
+        <v>220</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" t="s">
+        <v>74</v>
+      </c>
+      <c r="H35" t="s">
+        <v>90</v>
+      </c>
+      <c r="I35" t="s">
+        <v>80</v>
+      </c>
+      <c r="J35" t="s">
         <v>81</v>
       </c>
-      <c r="D35" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" t="s">
-        <v>9</v>
-      </c>
-      <c r="G35" t="s">
-        <v>86</v>
-      </c>
-      <c r="H35" t="s">
-        <v>100</v>
-      </c>
-      <c r="I35" t="s">
-        <v>96</v>
-      </c>
-      <c r="J35" t="s">
-        <v>97</v>
-      </c>
       <c r="K35" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3778,39 +3778,39 @@
       <c r="N35"/>
       <c r="O35"/>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B36">
-        <v>40565</v>
+        <v>40543</v>
       </c>
       <c r="C36" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" t="s">
+        <v>80</v>
+      </c>
+      <c r="J36" t="s">
         <v>81</v>
       </c>
-      <c r="D36" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" t="s">
-        <v>9</v>
-      </c>
-      <c r="G36" t="s">
-        <v>82</v>
-      </c>
-      <c r="H36" t="s">
-        <v>41</v>
-      </c>
-      <c r="I36" t="s">
-        <v>84</v>
-      </c>
-      <c r="J36" t="s">
-        <v>85</v>
-      </c>
       <c r="K36" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3819,18 +3819,18 @@
       <c r="N36"/>
       <c r="O36"/>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B37">
-        <v>40566</v>
+        <v>40551</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>220</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -3839,19 +3839,19 @@
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H37" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s">
+        <v>83</v>
+      </c>
+      <c r="J37" t="s">
         <v>84</v>
       </c>
-      <c r="J37" t="s">
-        <v>85</v>
-      </c>
       <c r="K37" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3860,39 +3860,39 @@
       <c r="N37"/>
       <c r="O37"/>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B38">
-        <v>40567</v>
+        <v>40555</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>220</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="I38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K38" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3901,39 +3901,39 @@
       <c r="N38"/>
       <c r="O38"/>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B39">
-        <v>40568</v>
+        <v>40681</v>
       </c>
       <c r="C39" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>220</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H39" t="s">
+        <v>56</v>
+      </c>
+      <c r="I39" t="s">
+        <v>100</v>
+      </c>
+      <c r="J39" t="s">
         <v>101</v>
       </c>
-      <c r="I39" t="s">
-        <v>84</v>
-      </c>
-      <c r="J39" t="s">
-        <v>85</v>
-      </c>
       <c r="K39" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -3942,39 +3942,39 @@
       <c r="N39"/>
       <c r="O39"/>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B40">
-        <v>40569</v>
+        <v>40526</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>221</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I40" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J40" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -3983,39 +3983,39 @@
       <c r="N40"/>
       <c r="O40"/>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B41">
-        <v>40570</v>
+        <v>40528</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="I41" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J41" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4024,18 +4024,18 @@
       <c r="N41"/>
       <c r="O41"/>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B42">
-        <v>40571</v>
+        <v>40530</v>
       </c>
       <c r="C42" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>221</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -4044,19 +4044,19 @@
         <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="I42" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J42" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4065,18 +4065,18 @@
       <c r="N42"/>
       <c r="O42"/>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B43">
-        <v>40572</v>
+        <v>40532</v>
       </c>
       <c r="C43" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -4085,19 +4085,19 @@
         <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="I43" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J43" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4106,39 +4106,39 @@
       <c r="N43"/>
       <c r="O43"/>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B44">
-        <v>40573</v>
+        <v>40540</v>
       </c>
       <c r="C44" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" t="s">
+        <v>221</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" t="s">
+        <v>40</v>
+      </c>
+      <c r="I44" t="s">
+        <v>80</v>
+      </c>
+      <c r="J44" t="s">
         <v>81</v>
       </c>
-      <c r="D44" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>9</v>
-      </c>
-      <c r="G44" t="s">
-        <v>82</v>
-      </c>
-      <c r="H44" t="s">
-        <v>66</v>
-      </c>
-      <c r="I44" t="s">
-        <v>84</v>
-      </c>
-      <c r="J44" t="s">
-        <v>85</v>
-      </c>
       <c r="K44" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4147,18 +4147,18 @@
       <c r="N44"/>
       <c r="O44"/>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B45">
-        <v>40574</v>
+        <v>40542</v>
       </c>
       <c r="C45" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4167,19 +4167,19 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I45" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J45" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4188,39 +4188,39 @@
       <c r="N45"/>
       <c r="O45"/>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B46">
-        <v>40585</v>
+        <v>40544</v>
       </c>
       <c r="C46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" t="s">
+        <v>44</v>
+      </c>
+      <c r="I46" t="s">
+        <v>80</v>
+      </c>
+      <c r="J46" t="s">
         <v>81</v>
       </c>
-      <c r="D46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E46" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" t="s">
-        <v>82</v>
-      </c>
-      <c r="H46" t="s">
-        <v>64</v>
-      </c>
-      <c r="I46" t="s">
-        <v>88</v>
-      </c>
-      <c r="J46" t="s">
-        <v>89</v>
-      </c>
       <c r="K46" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4229,18 +4229,18 @@
       <c r="N46"/>
       <c r="O46"/>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B47">
-        <v>40586</v>
+        <v>40552</v>
       </c>
       <c r="C47" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
@@ -4249,19 +4249,19 @@
         <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="K47" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4270,18 +4270,18 @@
       <c r="N47"/>
       <c r="O47"/>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B48">
-        <v>40587</v>
+        <v>40556</v>
       </c>
       <c r="C48" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>221</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -4290,19 +4290,19 @@
         <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="I48" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J48" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K48" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4311,39 +4311,39 @@
       <c r="N48"/>
       <c r="O48"/>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B49">
-        <v>40588</v>
+        <v>40493</v>
       </c>
       <c r="C49" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="E49" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F49" t="s">
         <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="I49" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J49" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -4352,18 +4352,18 @@
       <c r="N49"/>
       <c r="O49"/>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B50">
-        <v>40589</v>
+        <v>40495</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>222</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
@@ -4372,19 +4372,19 @@
         <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H50" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="I50" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J50" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K50" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -4393,39 +4393,39 @@
       <c r="N50"/>
       <c r="O50"/>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B51">
-        <v>40590</v>
+        <v>40501</v>
       </c>
       <c r="C51" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" t="s">
+        <v>222</v>
+      </c>
+      <c r="E51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G51" t="s">
+        <v>74</v>
+      </c>
+      <c r="H51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I51" t="s">
+        <v>80</v>
+      </c>
+      <c r="J51" t="s">
         <v>81</v>
       </c>
-      <c r="D51" t="s">
-        <v>49</v>
-      </c>
-      <c r="E51" t="s">
-        <v>19</v>
-      </c>
-      <c r="F51" t="s">
-        <v>9</v>
-      </c>
-      <c r="G51" t="s">
-        <v>86</v>
-      </c>
-      <c r="H51" t="s">
-        <v>44</v>
-      </c>
-      <c r="I51" t="s">
-        <v>88</v>
-      </c>
-      <c r="J51" t="s">
-        <v>89</v>
-      </c>
       <c r="K51" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -4434,39 +4434,39 @@
       <c r="N51"/>
       <c r="O51"/>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B52">
-        <v>40591</v>
+        <v>40503</v>
       </c>
       <c r="C52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52" t="s">
+        <v>222</v>
+      </c>
+      <c r="E52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" t="s">
+        <v>9</v>
+      </c>
+      <c r="G52" t="s">
+        <v>74</v>
+      </c>
+      <c r="H52" t="s">
+        <v>79</v>
+      </c>
+      <c r="I52" t="s">
+        <v>80</v>
+      </c>
+      <c r="J52" t="s">
         <v>81</v>
       </c>
-      <c r="D52" t="s">
-        <v>46</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>9</v>
-      </c>
-      <c r="G52" t="s">
-        <v>82</v>
-      </c>
-      <c r="H52" t="s">
-        <v>66</v>
-      </c>
-      <c r="I52" t="s">
-        <v>88</v>
-      </c>
-      <c r="J52" t="s">
-        <v>89</v>
-      </c>
       <c r="K52" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -4475,39 +4475,39 @@
       <c r="N52"/>
       <c r="O52"/>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B53">
-        <v>40592</v>
+        <v>40505</v>
       </c>
       <c r="C53" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" t="s">
+        <v>222</v>
+      </c>
+      <c r="E53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" t="s">
+        <v>74</v>
+      </c>
+      <c r="H53" t="s">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s">
+        <v>80</v>
+      </c>
+      <c r="J53" t="s">
         <v>81</v>
       </c>
-      <c r="D53" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>9</v>
-      </c>
-      <c r="G53" t="s">
-        <v>86</v>
-      </c>
-      <c r="H53" t="s">
-        <v>66</v>
-      </c>
-      <c r="I53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J53" t="s">
-        <v>89</v>
-      </c>
       <c r="K53" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4516,18 +4516,18 @@
       <c r="N53"/>
       <c r="O53"/>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B54">
-        <v>40593</v>
+        <v>40513</v>
       </c>
       <c r="C54" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
+        <v>222</v>
       </c>
       <c r="E54" t="s">
         <v>19</v>
@@ -4536,19 +4536,19 @@
         <v>9</v>
       </c>
       <c r="G54" t="s">
+        <v>74</v>
+      </c>
+      <c r="H54" t="s">
         <v>82</v>
       </c>
-      <c r="H54" t="s">
-        <v>102</v>
-      </c>
       <c r="I54" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J54" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="K54" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -4557,39 +4557,39 @@
       <c r="N54"/>
       <c r="O54"/>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B55">
-        <v>40594</v>
+        <v>40517</v>
       </c>
       <c r="C55" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="E55" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F55" t="s">
         <v>9</v>
       </c>
       <c r="G55" t="s">
+        <v>74</v>
+      </c>
+      <c r="H55" t="s">
+        <v>59</v>
+      </c>
+      <c r="I55" t="s">
+        <v>85</v>
+      </c>
+      <c r="J55" t="s">
         <v>86</v>
       </c>
-      <c r="H55" t="s">
-        <v>102</v>
-      </c>
-      <c r="I55" t="s">
-        <v>88</v>
-      </c>
-      <c r="J55" t="s">
-        <v>89</v>
-      </c>
       <c r="K55" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -4598,39 +4598,39 @@
       <c r="N55"/>
       <c r="O55"/>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B56">
-        <v>40595</v>
+        <v>40679</v>
       </c>
       <c r="C56" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>222</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F56" t="s">
         <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="H56" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I56" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J56" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="K56" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -4639,18 +4639,18 @@
       <c r="N56"/>
       <c r="O56"/>
     </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B57">
-        <v>40596</v>
+        <v>40494</v>
       </c>
       <c r="C57" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D57" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
@@ -4659,19 +4659,19 @@
         <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="I57" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J57" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K57" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -4680,39 +4680,39 @@
       <c r="N57"/>
       <c r="O57"/>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B58">
-        <v>40611</v>
+        <v>40496</v>
       </c>
       <c r="C58" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
+        <v>223</v>
       </c>
       <c r="E58" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
         <v>9</v>
       </c>
       <c r="G58" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I58" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J58" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K58" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -4721,39 +4721,39 @@
       <c r="N58"/>
       <c r="O58"/>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B59">
-        <v>40612</v>
+        <v>40502</v>
       </c>
       <c r="C59" t="s">
+        <v>73</v>
+      </c>
+      <c r="D59" t="s">
+        <v>223</v>
+      </c>
+      <c r="E59" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" t="s">
+        <v>9</v>
+      </c>
+      <c r="G59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H59" t="s">
+        <v>75</v>
+      </c>
+      <c r="I59" t="s">
+        <v>80</v>
+      </c>
+      <c r="J59" t="s">
         <v>81</v>
       </c>
-      <c r="D59" t="s">
-        <v>49</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>9</v>
-      </c>
-      <c r="G59" t="s">
-        <v>86</v>
-      </c>
-      <c r="H59" t="s">
-        <v>66</v>
-      </c>
-      <c r="I59" t="s">
-        <v>93</v>
-      </c>
-      <c r="J59" t="s">
-        <v>94</v>
-      </c>
       <c r="K59" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -4762,39 +4762,39 @@
       <c r="N59"/>
       <c r="O59"/>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B60">
-        <v>40619</v>
+        <v>40504</v>
       </c>
       <c r="C60" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" t="s">
+        <v>223</v>
+      </c>
+      <c r="E60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" t="s">
+        <v>9</v>
+      </c>
+      <c r="G60" t="s">
+        <v>78</v>
+      </c>
+      <c r="H60" t="s">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s">
+        <v>80</v>
+      </c>
+      <c r="J60" t="s">
         <v>81</v>
       </c>
-      <c r="D60" t="s">
-        <v>55</v>
-      </c>
-      <c r="E60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" t="s">
-        <v>9</v>
-      </c>
-      <c r="G60" t="s">
-        <v>82</v>
-      </c>
-      <c r="H60" t="s">
-        <v>103</v>
-      </c>
-      <c r="I60" t="s">
-        <v>96</v>
-      </c>
-      <c r="J60" t="s">
-        <v>97</v>
-      </c>
       <c r="K60" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -4803,39 +4803,39 @@
       <c r="N60"/>
       <c r="O60"/>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>50</v>
       </c>
       <c r="B61">
-        <v>40620</v>
+        <v>40506</v>
       </c>
       <c r="C61" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" t="s">
+        <v>19</v>
+      </c>
+      <c r="F61" t="s">
+        <v>9</v>
+      </c>
+      <c r="G61" t="s">
+        <v>78</v>
+      </c>
+      <c r="H61" t="s">
+        <v>82</v>
+      </c>
+      <c r="I61" t="s">
+        <v>80</v>
+      </c>
+      <c r="J61" t="s">
         <v>81</v>
       </c>
-      <c r="D61" t="s">
-        <v>51</v>
-      </c>
-      <c r="E61" t="s">
-        <v>19</v>
-      </c>
-      <c r="F61" t="s">
-        <v>9</v>
-      </c>
-      <c r="G61" t="s">
-        <v>86</v>
-      </c>
-      <c r="H61" t="s">
-        <v>103</v>
-      </c>
-      <c r="I61" t="s">
-        <v>96</v>
-      </c>
-      <c r="J61" t="s">
-        <v>97</v>
-      </c>
       <c r="K61" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -4844,18 +4844,18 @@
       <c r="N61"/>
       <c r="O61"/>
     </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B62">
-        <v>40621</v>
+        <v>40514</v>
       </c>
       <c r="C62" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>55</v>
+        <v>223</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
@@ -4864,19 +4864,19 @@
         <v>9</v>
       </c>
       <c r="G62" t="s">
+        <v>78</v>
+      </c>
+      <c r="H62" t="s">
         <v>82</v>
       </c>
-      <c r="H62" t="s">
-        <v>53</v>
-      </c>
       <c r="I62" t="s">
+        <v>83</v>
+      </c>
+      <c r="J62" t="s">
         <v>84</v>
       </c>
-      <c r="J62" t="s">
-        <v>85</v>
-      </c>
       <c r="K62" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -4885,39 +4885,39 @@
       <c r="N62"/>
       <c r="O62"/>
     </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>50</v>
       </c>
       <c r="B63">
-        <v>40622</v>
+        <v>40518</v>
       </c>
       <c r="C63" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>223</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F63" t="s">
         <v>9</v>
       </c>
       <c r="G63" t="s">
+        <v>78</v>
+      </c>
+      <c r="H63" t="s">
+        <v>59</v>
+      </c>
+      <c r="I63" t="s">
+        <v>85</v>
+      </c>
+      <c r="J63" t="s">
         <v>86</v>
       </c>
-      <c r="H63" t="s">
-        <v>53</v>
-      </c>
-      <c r="I63" t="s">
-        <v>84</v>
-      </c>
-      <c r="J63" t="s">
-        <v>85</v>
-      </c>
       <c r="K63" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -4926,39 +4926,39 @@
       <c r="N63"/>
       <c r="O63"/>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B64">
-        <v>40623</v>
+        <v>40619</v>
       </c>
       <c r="C64" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D64" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="E64" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F64" t="s">
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H64" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="I64" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J64" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -4967,39 +4967,39 @@
       <c r="N64"/>
       <c r="O64"/>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B65">
-        <v>40624</v>
+        <v>40621</v>
       </c>
       <c r="C65" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>224</v>
       </c>
       <c r="E65" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F65" t="s">
         <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H65" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="I65" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J65" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K65" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5008,39 +5008,39 @@
       <c r="N65"/>
       <c r="O65"/>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B66">
-        <v>40625</v>
+        <v>40623</v>
       </c>
       <c r="C66" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D66" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F66" t="s">
         <v>9</v>
       </c>
       <c r="G66" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I66" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J66" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K66" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -5049,39 +5049,39 @@
       <c r="N66"/>
       <c r="O66"/>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B67">
-        <v>40626</v>
+        <v>40625</v>
       </c>
       <c r="C67" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D67" t="s">
+        <v>224</v>
+      </c>
+      <c r="E67" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" t="s">
+        <v>9</v>
+      </c>
+      <c r="G67" t="s">
+        <v>74</v>
+      </c>
+      <c r="H67" t="s">
         <v>51</v>
       </c>
-      <c r="E67" t="s">
-        <v>19</v>
-      </c>
-      <c r="F67" t="s">
-        <v>9</v>
-      </c>
-      <c r="G67" t="s">
-        <v>86</v>
-      </c>
-      <c r="H67" t="s">
-        <v>58</v>
-      </c>
       <c r="I67" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J67" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -5090,18 +5090,18 @@
       <c r="N67"/>
       <c r="O67"/>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B68">
         <v>40627</v>
       </c>
       <c r="C68" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
@@ -5110,19 +5110,19 @@
         <v>9</v>
       </c>
       <c r="G68" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H68" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I68" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J68" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K68" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -5131,18 +5131,18 @@
       <c r="N68"/>
       <c r="O68"/>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B69">
-        <v>40628</v>
+        <v>40629</v>
       </c>
       <c r="C69" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>51</v>
+        <v>224</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
@@ -5151,19 +5151,19 @@
         <v>9</v>
       </c>
       <c r="G69" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H69" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="I69" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J69" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K69" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -5172,18 +5172,18 @@
       <c r="N69"/>
       <c r="O69"/>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B70">
-        <v>40629</v>
+        <v>40631</v>
       </c>
       <c r="C70" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D70" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="E70" t="s">
         <v>19</v>
@@ -5192,19 +5192,19 @@
         <v>9</v>
       </c>
       <c r="G70" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H70" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="I70" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J70" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K70" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -5213,39 +5213,39 @@
       <c r="N70"/>
       <c r="O70"/>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B71">
-        <v>40630</v>
+        <v>40641</v>
       </c>
       <c r="C71" t="s">
+        <v>73</v>
+      </c>
+      <c r="D71" t="s">
+        <v>224</v>
+      </c>
+      <c r="E71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G71" t="s">
+        <v>74</v>
+      </c>
+      <c r="H71" t="s">
+        <v>48</v>
+      </c>
+      <c r="I71" t="s">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s">
         <v>81</v>
       </c>
-      <c r="D71" t="s">
-        <v>51</v>
-      </c>
-      <c r="E71" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" t="s">
-        <v>9</v>
-      </c>
-      <c r="G71" t="s">
-        <v>86</v>
-      </c>
-      <c r="H71" t="s">
-        <v>104</v>
-      </c>
-      <c r="I71" t="s">
-        <v>84</v>
-      </c>
-      <c r="J71" t="s">
-        <v>85</v>
-      </c>
       <c r="K71" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -5254,39 +5254,39 @@
       <c r="N71"/>
       <c r="O71"/>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B72">
-        <v>40631</v>
+        <v>40643</v>
       </c>
       <c r="C72" t="s">
+        <v>73</v>
+      </c>
+      <c r="D72" t="s">
+        <v>224</v>
+      </c>
+      <c r="E72" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" t="s">
+        <v>9</v>
+      </c>
+      <c r="G72" t="s">
+        <v>74</v>
+      </c>
+      <c r="H72" t="s">
+        <v>57</v>
+      </c>
+      <c r="I72" t="s">
+        <v>80</v>
+      </c>
+      <c r="J72" t="s">
         <v>81</v>
       </c>
-      <c r="D72" t="s">
-        <v>55</v>
-      </c>
-      <c r="E72" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" t="s">
-        <v>9</v>
-      </c>
-      <c r="G72" t="s">
-        <v>82</v>
-      </c>
-      <c r="H72" t="s">
-        <v>59</v>
-      </c>
-      <c r="I72" t="s">
-        <v>84</v>
-      </c>
-      <c r="J72" t="s">
-        <v>85</v>
-      </c>
       <c r="K72" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -5295,39 +5295,39 @@
       <c r="N72"/>
       <c r="O72"/>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B73">
-        <v>40632</v>
+        <v>40645</v>
       </c>
       <c r="C73" t="s">
+        <v>73</v>
+      </c>
+      <c r="D73" t="s">
+        <v>224</v>
+      </c>
+      <c r="E73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G73" t="s">
+        <v>74</v>
+      </c>
+      <c r="H73" t="s">
+        <v>51</v>
+      </c>
+      <c r="I73" t="s">
+        <v>80</v>
+      </c>
+      <c r="J73" t="s">
         <v>81</v>
       </c>
-      <c r="D73" t="s">
-        <v>51</v>
-      </c>
-      <c r="E73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" t="s">
-        <v>9</v>
-      </c>
-      <c r="G73" t="s">
-        <v>86</v>
-      </c>
-      <c r="H73" t="s">
-        <v>59</v>
-      </c>
-      <c r="I73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J73" t="s">
-        <v>85</v>
-      </c>
       <c r="K73" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -5336,39 +5336,39 @@
       <c r="N73"/>
       <c r="O73"/>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B74">
-        <v>40641</v>
+        <v>40647</v>
       </c>
       <c r="C74" t="s">
+        <v>73</v>
+      </c>
+      <c r="D74" t="s">
+        <v>224</v>
+      </c>
+      <c r="E74" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G74" t="s">
+        <v>74</v>
+      </c>
+      <c r="H74" t="s">
+        <v>93</v>
+      </c>
+      <c r="I74" t="s">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s">
         <v>81</v>
       </c>
-      <c r="D74" t="s">
-        <v>55</v>
-      </c>
-      <c r="E74" t="s">
-        <v>19</v>
-      </c>
-      <c r="F74" t="s">
-        <v>9</v>
-      </c>
-      <c r="G74" t="s">
-        <v>82</v>
-      </c>
-      <c r="H74" t="s">
-        <v>53</v>
-      </c>
-      <c r="I74" t="s">
-        <v>88</v>
-      </c>
-      <c r="J74" t="s">
-        <v>89</v>
-      </c>
       <c r="K74" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -5377,39 +5377,39 @@
       <c r="N74"/>
       <c r="O74"/>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B75">
-        <v>40642</v>
+        <v>40649</v>
       </c>
       <c r="C75" t="s">
+        <v>73</v>
+      </c>
+      <c r="D75" t="s">
+        <v>224</v>
+      </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>9</v>
+      </c>
+      <c r="G75" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" t="s">
+        <v>47</v>
+      </c>
+      <c r="I75" t="s">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s">
         <v>81</v>
       </c>
-      <c r="D75" t="s">
-        <v>51</v>
-      </c>
-      <c r="E75" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" t="s">
-        <v>9</v>
-      </c>
-      <c r="G75" t="s">
-        <v>86</v>
-      </c>
-      <c r="H75" t="s">
-        <v>53</v>
-      </c>
-      <c r="I75" t="s">
-        <v>88</v>
-      </c>
-      <c r="J75" t="s">
-        <v>89</v>
-      </c>
       <c r="K75" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -5418,39 +5418,39 @@
       <c r="N75"/>
       <c r="O75"/>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B76">
-        <v>40643</v>
+        <v>40651</v>
       </c>
       <c r="C76" t="s">
+        <v>73</v>
+      </c>
+      <c r="D76" t="s">
+        <v>224</v>
+      </c>
+      <c r="E76" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" t="s">
+        <v>9</v>
+      </c>
+      <c r="G76" t="s">
+        <v>74</v>
+      </c>
+      <c r="H76" t="s">
+        <v>96</v>
+      </c>
+      <c r="I76" t="s">
+        <v>80</v>
+      </c>
+      <c r="J76" t="s">
         <v>81</v>
       </c>
-      <c r="D76" t="s">
-        <v>55</v>
-      </c>
-      <c r="E76" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" t="s">
-        <v>9</v>
-      </c>
-      <c r="G76" t="s">
-        <v>82</v>
-      </c>
-      <c r="H76" t="s">
-        <v>65</v>
-      </c>
-      <c r="I76" t="s">
-        <v>88</v>
-      </c>
-      <c r="J76" t="s">
-        <v>89</v>
-      </c>
       <c r="K76" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -5459,39 +5459,39 @@
       <c r="N76"/>
       <c r="O76"/>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B77">
-        <v>40644</v>
+        <v>40653</v>
       </c>
       <c r="C77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D77" t="s">
+        <v>224</v>
+      </c>
+      <c r="E77" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" t="s">
+        <v>9</v>
+      </c>
+      <c r="G77" t="s">
+        <v>74</v>
+      </c>
+      <c r="H77" t="s">
+        <v>52</v>
+      </c>
+      <c r="I77" t="s">
+        <v>80</v>
+      </c>
+      <c r="J77" t="s">
         <v>81</v>
       </c>
-      <c r="D77" t="s">
-        <v>51</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>9</v>
-      </c>
-      <c r="G77" t="s">
-        <v>86</v>
-      </c>
-      <c r="H77" t="s">
-        <v>65</v>
-      </c>
-      <c r="I77" t="s">
-        <v>88</v>
-      </c>
-      <c r="J77" t="s">
-        <v>89</v>
-      </c>
       <c r="K77" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -5500,18 +5500,18 @@
       <c r="N77"/>
       <c r="O77"/>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B78">
-        <v>40645</v>
+        <v>40669</v>
       </c>
       <c r="C78" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D78" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
@@ -5520,19 +5520,19 @@
         <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H78" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="I78" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J78" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K78" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -5541,39 +5541,39 @@
       <c r="N78"/>
       <c r="O78"/>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B79">
-        <v>40646</v>
+        <v>40673</v>
       </c>
       <c r="C79" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D79" t="s">
-        <v>51</v>
+        <v>224</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
       </c>
       <c r="G79" t="s">
+        <v>74</v>
+      </c>
+      <c r="H79" t="s">
+        <v>47</v>
+      </c>
+      <c r="I79" t="s">
+        <v>85</v>
+      </c>
+      <c r="J79" t="s">
         <v>86</v>
       </c>
-      <c r="H79" t="s">
-        <v>58</v>
-      </c>
-      <c r="I79" t="s">
-        <v>88</v>
-      </c>
-      <c r="J79" t="s">
-        <v>89</v>
-      </c>
       <c r="K79" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -5582,39 +5582,39 @@
       <c r="N79"/>
       <c r="O79"/>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B80">
-        <v>40647</v>
+        <v>40675</v>
       </c>
       <c r="C80" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D80" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="E80" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F80" t="s">
         <v>9</v>
       </c>
       <c r="G80" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H80" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="I80" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="J80" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K80" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -5623,39 +5623,39 @@
       <c r="N80"/>
       <c r="O80"/>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B81">
-        <v>40648</v>
+        <v>40685</v>
       </c>
       <c r="C81" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D81" t="s">
-        <v>51</v>
+        <v>224</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F81" t="s">
         <v>9</v>
       </c>
       <c r="G81" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H81" t="s">
+        <v>93</v>
+      </c>
+      <c r="I81" t="s">
+        <v>100</v>
+      </c>
+      <c r="J81" t="s">
         <v>101</v>
       </c>
-      <c r="I81" t="s">
-        <v>88</v>
-      </c>
-      <c r="J81" t="s">
-        <v>89</v>
-      </c>
       <c r="K81" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -5664,39 +5664,39 @@
       <c r="N81"/>
       <c r="O81"/>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B82">
-        <v>40649</v>
+        <v>40686</v>
       </c>
       <c r="C82" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D82" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
       </c>
       <c r="G82" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="H82" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I82" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J82" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="K82" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -5705,18 +5705,18 @@
       <c r="N82"/>
       <c r="O82"/>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B83">
-        <v>40650</v>
+        <v>40620</v>
       </c>
       <c r="C83" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D83" t="s">
-        <v>51</v>
+        <v>225</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
@@ -5725,10 +5725,10 @@
         <v>9</v>
       </c>
       <c r="G83" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="I83" t="s">
         <v>88</v>
@@ -5737,7 +5737,7 @@
         <v>89</v>
       </c>
       <c r="K83" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -5746,18 +5746,18 @@
       <c r="N83"/>
       <c r="O83"/>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B84">
-        <v>40651</v>
+        <v>40622</v>
       </c>
       <c r="C84" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D84" t="s">
-        <v>55</v>
+        <v>225</v>
       </c>
       <c r="E84" t="s">
         <v>19</v>
@@ -5766,19 +5766,19 @@
         <v>9</v>
       </c>
       <c r="G84" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="I84" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J84" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K84" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -5787,39 +5787,39 @@
       <c r="N84"/>
       <c r="O84"/>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B85">
-        <v>40652</v>
+        <v>40624</v>
       </c>
       <c r="C85" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D85" t="s">
-        <v>51</v>
+        <v>225</v>
       </c>
       <c r="E85" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F85" t="s">
         <v>9</v>
       </c>
       <c r="G85" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H85" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="I85" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J85" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K85" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -5828,18 +5828,18 @@
       <c r="N85"/>
       <c r="O85"/>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B86">
-        <v>40653</v>
+        <v>40626</v>
       </c>
       <c r="C86" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>55</v>
+        <v>225</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
@@ -5848,19 +5848,19 @@
         <v>9</v>
       </c>
       <c r="G86" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H86" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I86" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J86" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K86" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -5869,18 +5869,18 @@
       <c r="N86"/>
       <c r="O86"/>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B87">
-        <v>40654</v>
+        <v>40628</v>
       </c>
       <c r="C87" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D87" t="s">
-        <v>51</v>
+        <v>225</v>
       </c>
       <c r="E87" t="s">
         <v>19</v>
@@ -5889,19 +5889,19 @@
         <v>9</v>
       </c>
       <c r="G87" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H87" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="I87" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J87" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K87" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -5910,18 +5910,18 @@
       <c r="N87"/>
       <c r="O87"/>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B88">
-        <v>40669</v>
+        <v>40630</v>
       </c>
       <c r="C88" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D88" t="s">
-        <v>55</v>
+        <v>225</v>
       </c>
       <c r="E88" t="s">
         <v>19</v>
@@ -5930,19 +5930,19 @@
         <v>9</v>
       </c>
       <c r="G88" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H88" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I88" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J88" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K88" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -5951,18 +5951,18 @@
       <c r="N88"/>
       <c r="O88"/>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B89">
-        <v>40670</v>
+        <v>40632</v>
       </c>
       <c r="C89" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D89" t="s">
-        <v>51</v>
+        <v>225</v>
       </c>
       <c r="E89" t="s">
         <v>19</v>
@@ -5971,19 +5971,19 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H89" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="I89" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J89" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K89" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -5992,39 +5992,39 @@
       <c r="N89"/>
       <c r="O89"/>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B90">
-        <v>40673</v>
+        <v>40642</v>
       </c>
       <c r="C90" t="s">
+        <v>73</v>
+      </c>
+      <c r="D90" t="s">
+        <v>225</v>
+      </c>
+      <c r="E90" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90" t="s">
+        <v>9</v>
+      </c>
+      <c r="G90" t="s">
+        <v>78</v>
+      </c>
+      <c r="H90" t="s">
+        <v>48</v>
+      </c>
+      <c r="I90" t="s">
+        <v>80</v>
+      </c>
+      <c r="J90" t="s">
         <v>81</v>
       </c>
-      <c r="D90" t="s">
-        <v>55</v>
-      </c>
-      <c r="E90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" t="s">
-        <v>9</v>
-      </c>
-      <c r="G90" t="s">
-        <v>82</v>
-      </c>
-      <c r="H90" t="s">
-        <v>52</v>
-      </c>
-      <c r="I90" t="s">
-        <v>93</v>
-      </c>
-      <c r="J90" t="s">
-        <v>94</v>
-      </c>
       <c r="K90" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -6033,18 +6033,18 @@
       <c r="N90"/>
       <c r="O90"/>
     </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B91">
-        <v>40674</v>
+        <v>40644</v>
       </c>
       <c r="C91" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D91" t="s">
-        <v>51</v>
+        <v>225</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -6053,19 +6053,19 @@
         <v>9</v>
       </c>
       <c r="G91" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I91" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J91" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K91" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -6074,39 +6074,39 @@
       <c r="N91"/>
       <c r="O91"/>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B92">
-        <v>40675</v>
+        <v>40646</v>
       </c>
       <c r="C92" t="s">
+        <v>73</v>
+      </c>
+      <c r="D92" t="s">
+        <v>225</v>
+      </c>
+      <c r="E92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" t="s">
+        <v>9</v>
+      </c>
+      <c r="G92" t="s">
+        <v>78</v>
+      </c>
+      <c r="H92" t="s">
+        <v>51</v>
+      </c>
+      <c r="I92" t="s">
+        <v>80</v>
+      </c>
+      <c r="J92" t="s">
         <v>81</v>
       </c>
-      <c r="D92" t="s">
-        <v>55</v>
-      </c>
-      <c r="E92" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" t="s">
-        <v>9</v>
-      </c>
-      <c r="G92" t="s">
-        <v>82</v>
-      </c>
-      <c r="H92" t="s">
-        <v>67</v>
-      </c>
-      <c r="I92" t="s">
-        <v>105</v>
-      </c>
-      <c r="J92" t="s">
-        <v>106</v>
-      </c>
       <c r="K92" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -6115,39 +6115,39 @@
       <c r="N92"/>
       <c r="O92"/>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B93">
-        <v>40676</v>
+        <v>40648</v>
       </c>
       <c r="C93" t="s">
+        <v>73</v>
+      </c>
+      <c r="D93" t="s">
+        <v>225</v>
+      </c>
+      <c r="E93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F93" t="s">
+        <v>9</v>
+      </c>
+      <c r="G93" t="s">
+        <v>78</v>
+      </c>
+      <c r="H93" t="s">
+        <v>93</v>
+      </c>
+      <c r="I93" t="s">
+        <v>80</v>
+      </c>
+      <c r="J93" t="s">
         <v>81</v>
       </c>
-      <c r="D93" t="s">
-        <v>51</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>9</v>
-      </c>
-      <c r="G93" t="s">
-        <v>86</v>
-      </c>
-      <c r="H93" t="s">
-        <v>67</v>
-      </c>
-      <c r="I93" t="s">
-        <v>105</v>
-      </c>
-      <c r="J93" t="s">
-        <v>106</v>
-      </c>
       <c r="K93" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -6156,39 +6156,39 @@
       <c r="N93"/>
       <c r="O93"/>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B94">
-        <v>40679</v>
+        <v>40650</v>
       </c>
       <c r="C94" t="s">
+        <v>73</v>
+      </c>
+      <c r="D94" t="s">
+        <v>225</v>
+      </c>
+      <c r="E94" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" t="s">
+        <v>9</v>
+      </c>
+      <c r="G94" t="s">
+        <v>78</v>
+      </c>
+      <c r="H94" t="s">
+        <v>47</v>
+      </c>
+      <c r="I94" t="s">
+        <v>80</v>
+      </c>
+      <c r="J94" t="s">
         <v>81</v>
       </c>
-      <c r="D94" t="s">
-        <v>40</v>
-      </c>
-      <c r="E94" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" t="s">
-        <v>9</v>
-      </c>
-      <c r="G94" t="s">
-        <v>107</v>
-      </c>
-      <c r="H94" t="s">
-        <v>67</v>
-      </c>
-      <c r="I94" t="s">
-        <v>108</v>
-      </c>
-      <c r="J94" t="s">
-        <v>109</v>
-      </c>
       <c r="K94" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -6197,39 +6197,39 @@
       <c r="N94"/>
       <c r="O94"/>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B95">
-        <v>40681</v>
+        <v>40652</v>
       </c>
       <c r="C95" t="s">
+        <v>73</v>
+      </c>
+      <c r="D95" t="s">
+        <v>225</v>
+      </c>
+      <c r="E95" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" t="s">
+        <v>9</v>
+      </c>
+      <c r="G95" t="s">
+        <v>78</v>
+      </c>
+      <c r="H95" t="s">
+        <v>96</v>
+      </c>
+      <c r="I95" t="s">
+        <v>80</v>
+      </c>
+      <c r="J95" t="s">
         <v>81</v>
       </c>
-      <c r="D95" t="s">
-        <v>43</v>
-      </c>
-      <c r="E95" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" t="s">
-        <v>9</v>
-      </c>
-      <c r="G95" t="s">
-        <v>107</v>
-      </c>
-      <c r="H95" t="s">
-        <v>64</v>
-      </c>
-      <c r="I95" t="s">
-        <v>108</v>
-      </c>
-      <c r="J95" t="s">
-        <v>109</v>
-      </c>
       <c r="K95" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -6238,39 +6238,39 @@
       <c r="N95"/>
       <c r="O95"/>
     </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B96">
-        <v>40683</v>
+        <v>40654</v>
       </c>
       <c r="C96" t="s">
+        <v>73</v>
+      </c>
+      <c r="D96" t="s">
+        <v>225</v>
+      </c>
+      <c r="E96" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" t="s">
+        <v>9</v>
+      </c>
+      <c r="G96" t="s">
+        <v>78</v>
+      </c>
+      <c r="H96" t="s">
+        <v>52</v>
+      </c>
+      <c r="I96" t="s">
+        <v>80</v>
+      </c>
+      <c r="J96" t="s">
         <v>81</v>
       </c>
-      <c r="D96" t="s">
-        <v>46</v>
-      </c>
-      <c r="E96" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" t="s">
-        <v>9</v>
-      </c>
-      <c r="G96" t="s">
-        <v>107</v>
-      </c>
-      <c r="H96" t="s">
-        <v>95</v>
-      </c>
-      <c r="I96" t="s">
-        <v>108</v>
-      </c>
-      <c r="J96" t="s">
-        <v>109</v>
-      </c>
       <c r="K96" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -6279,39 +6279,39 @@
       <c r="N96"/>
       <c r="O96"/>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B97">
-        <v>40684</v>
+        <v>40670</v>
       </c>
       <c r="C97" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D97" t="s">
-        <v>46</v>
+        <v>225</v>
       </c>
       <c r="E97" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F97" t="s">
         <v>9</v>
       </c>
       <c r="G97" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="H97" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="I97" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="J97" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="K97" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -6320,18 +6320,18 @@
       <c r="N97"/>
       <c r="O97"/>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B98">
-        <v>40685</v>
+        <v>40674</v>
       </c>
       <c r="C98" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D98" t="s">
-        <v>55</v>
+        <v>225</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -6340,19 +6340,19 @@
         <v>9</v>
       </c>
       <c r="G98" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="H98" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="I98" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="J98" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="K98" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -6361,18 +6361,18 @@
       <c r="N98"/>
       <c r="O98"/>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B99">
-        <v>40686</v>
+        <v>40676</v>
       </c>
       <c r="C99" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D99" t="s">
-        <v>55</v>
+        <v>225</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -6381,19 +6381,19 @@
         <v>9</v>
       </c>
       <c r="G99" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="H99" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I99" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J99" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="K99" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -6402,18 +6402,18 @@
       <c r="N99"/>
       <c r="O99"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B100">
         <v>40687</v>
       </c>
       <c r="C100" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D100" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E100" t="s">
         <v>19</v>
@@ -6422,43 +6422,43 @@
         <v>9</v>
       </c>
       <c r="G100" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H100" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I100" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J100" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K100" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L100">
         <v>6</v>
       </c>
       <c r="M100" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N100" t="s">
         <v>13</v>
       </c>
       <c r="O100"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B101">
         <v>40689</v>
       </c>
       <c r="C101" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D101" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
@@ -6467,109 +6467,109 @@
         <v>9</v>
       </c>
       <c r="G101" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H101" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I101" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J101" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K101" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L101">
         <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N101" t="s">
         <v>13</v>
       </c>
       <c r="O101"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B102">
         <v>40693</v>
       </c>
       <c r="C102" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" t="s">
+        <v>208</v>
+      </c>
+      <c r="E102" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" t="s">
+        <v>9</v>
+      </c>
+      <c r="G102" t="s">
+        <v>99</v>
+      </c>
+      <c r="H102" t="s">
+        <v>53</v>
+      </c>
+      <c r="I102" t="s">
+        <v>76</v>
+      </c>
+      <c r="J102" t="s">
+        <v>77</v>
+      </c>
+      <c r="K102" t="s">
         <v>112</v>
-      </c>
-      <c r="D102" t="s">
-        <v>216</v>
-      </c>
-      <c r="E102" t="s">
-        <v>19</v>
-      </c>
-      <c r="F102" t="s">
-        <v>9</v>
-      </c>
-      <c r="G102" t="s">
-        <v>107</v>
-      </c>
-      <c r="H102" t="s">
-        <v>60</v>
-      </c>
-      <c r="I102" t="s">
-        <v>84</v>
-      </c>
-      <c r="J102" t="s">
-        <v>85</v>
-      </c>
-      <c r="K102" t="s">
-        <v>120</v>
       </c>
       <c r="L102">
         <v>3</v>
       </c>
       <c r="M102"/>
       <c r="N102" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O102" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B103">
         <v>40694</v>
       </c>
       <c r="C103" t="s">
+        <v>104</v>
+      </c>
+      <c r="D103" t="s">
+        <v>208</v>
+      </c>
+      <c r="E103" t="s">
+        <v>19</v>
+      </c>
+      <c r="F103" t="s">
+        <v>9</v>
+      </c>
+      <c r="G103" t="s">
+        <v>99</v>
+      </c>
+      <c r="H103" t="s">
+        <v>53</v>
+      </c>
+      <c r="I103" t="s">
+        <v>76</v>
+      </c>
+      <c r="J103" t="s">
+        <v>77</v>
+      </c>
+      <c r="K103" t="s">
         <v>112</v>
-      </c>
-      <c r="D103" t="s">
-        <v>216</v>
-      </c>
-      <c r="E103" t="s">
-        <v>19</v>
-      </c>
-      <c r="F103" t="s">
-        <v>9</v>
-      </c>
-      <c r="G103" t="s">
-        <v>107</v>
-      </c>
-      <c r="H103" t="s">
-        <v>60</v>
-      </c>
-      <c r="I103" t="s">
-        <v>84</v>
-      </c>
-      <c r="J103" t="s">
-        <v>85</v>
-      </c>
-      <c r="K103" t="s">
-        <v>120</v>
       </c>
       <c r="L103">
         <v>3</v>
@@ -6579,87 +6579,87 @@
         <v>13</v>
       </c>
       <c r="O103" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B104">
         <v>40696</v>
       </c>
       <c r="C104" t="s">
+        <v>104</v>
+      </c>
+      <c r="D104" t="s">
+        <v>208</v>
+      </c>
+      <c r="E104" t="s">
+        <v>19</v>
+      </c>
+      <c r="F104" t="s">
+        <v>9</v>
+      </c>
+      <c r="G104" t="s">
+        <v>99</v>
+      </c>
+      <c r="H104" t="s">
+        <v>114</v>
+      </c>
+      <c r="I104" t="s">
+        <v>80</v>
+      </c>
+      <c r="J104" t="s">
+        <v>81</v>
+      </c>
+      <c r="K104" t="s">
         <v>112</v>
-      </c>
-      <c r="D104" t="s">
-        <v>216</v>
-      </c>
-      <c r="E104" t="s">
-        <v>19</v>
-      </c>
-      <c r="F104" t="s">
-        <v>9</v>
-      </c>
-      <c r="G104" t="s">
-        <v>107</v>
-      </c>
-      <c r="H104" t="s">
-        <v>122</v>
-      </c>
-      <c r="I104" t="s">
-        <v>88</v>
-      </c>
-      <c r="J104" t="s">
-        <v>89</v>
-      </c>
-      <c r="K104" t="s">
-        <v>120</v>
       </c>
       <c r="L104">
         <v>3</v>
       </c>
       <c r="M104"/>
       <c r="N104" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O104" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B105">
         <v>40698</v>
       </c>
       <c r="C105" t="s">
+        <v>104</v>
+      </c>
+      <c r="D105" t="s">
+        <v>208</v>
+      </c>
+      <c r="E105" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105" t="s">
+        <v>9</v>
+      </c>
+      <c r="G105" t="s">
+        <v>99</v>
+      </c>
+      <c r="H105" t="s">
+        <v>114</v>
+      </c>
+      <c r="I105" t="s">
+        <v>80</v>
+      </c>
+      <c r="J105" t="s">
+        <v>81</v>
+      </c>
+      <c r="K105" t="s">
         <v>112</v>
-      </c>
-      <c r="D105" t="s">
-        <v>216</v>
-      </c>
-      <c r="E105" t="s">
-        <v>19</v>
-      </c>
-      <c r="F105" t="s">
-        <v>9</v>
-      </c>
-      <c r="G105" t="s">
-        <v>107</v>
-      </c>
-      <c r="H105" t="s">
-        <v>122</v>
-      </c>
-      <c r="I105" t="s">
-        <v>88</v>
-      </c>
-      <c r="J105" t="s">
-        <v>89</v>
-      </c>
-      <c r="K105" t="s">
-        <v>120</v>
       </c>
       <c r="L105">
         <v>3</v>
@@ -6669,21 +6669,21 @@
         <v>13</v>
       </c>
       <c r="O105" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B106">
         <v>40688</v>
       </c>
       <c r="C106" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D106" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E106" t="s">
         <v>19</v>
@@ -6692,43 +6692,43 @@
         <v>9</v>
       </c>
       <c r="G106" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H106" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I106" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J106" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K106" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L106">
         <v>6</v>
       </c>
       <c r="M106" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N106" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O106"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B107">
         <v>40690</v>
       </c>
       <c r="C107" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D107" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E107" t="s">
         <v>19</v>
@@ -6737,43 +6737,43 @@
         <v>9</v>
       </c>
       <c r="G107" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H107" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I107" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J107" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K107" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L107">
         <v>6</v>
       </c>
       <c r="M107" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N107" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O107"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B108">
         <v>40691</v>
       </c>
       <c r="C108" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D108" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E108" t="s">
         <v>19</v>
@@ -6782,43 +6782,43 @@
         <v>9</v>
       </c>
       <c r="G108" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H108" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I108" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J108" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K108" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L108">
         <v>3</v>
       </c>
       <c r="M108"/>
       <c r="N108" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O108" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B109">
         <v>40692</v>
       </c>
       <c r="C109" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D109" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E109" t="s">
         <v>19</v>
@@ -6827,19 +6827,19 @@
         <v>9</v>
       </c>
       <c r="G109" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H109" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I109" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J109" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K109" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L109">
         <v>3</v>
@@ -6849,21 +6849,21 @@
         <v>13</v>
       </c>
       <c r="O109" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B110">
         <v>40695</v>
       </c>
       <c r="C110" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D110" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E110" t="s">
         <v>19</v>
@@ -6872,43 +6872,43 @@
         <v>9</v>
       </c>
       <c r="G110" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H110" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="I110" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J110" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K110" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L110">
         <v>3</v>
       </c>
       <c r="M110"/>
       <c r="N110" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O110" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B111">
         <v>40697</v>
       </c>
       <c r="C111" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D111" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
@@ -6917,19 +6917,19 @@
         <v>9</v>
       </c>
       <c r="G111" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H111" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="I111" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J111" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K111" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L111">
         <v>3</v>
@@ -6939,21 +6939,21 @@
         <v>13</v>
       </c>
       <c r="O111" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B112">
         <v>40699</v>
       </c>
       <c r="C112" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D112" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -6962,43 +6962,43 @@
         <v>9</v>
       </c>
       <c r="G112" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H112" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I112" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="J112" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="K112" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="L112">
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="N112" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O112"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B113">
         <v>40700</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D113" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -7007,25 +7007,25 @@
         <v>9</v>
       </c>
       <c r="G113" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H113" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I113" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="J113" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="K113" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="L113">
         <v>3</v>
       </c>
       <c r="M113" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="N113" t="s">
         <v>13</v>
@@ -7052,25 +7052,25 @@
         <v>9</v>
       </c>
       <c r="G114" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H114" t="s">
         <v>10</v>
       </c>
       <c r="I114" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J114" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K114" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L114">
         <v>6</v>
       </c>
       <c r="M114" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="N114" t="s">
         <v>13</v>
@@ -7097,28 +7097,28 @@
         <v>9</v>
       </c>
       <c r="G115" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H115" t="s">
         <v>10</v>
       </c>
       <c r="I115" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J115" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K115" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L115">
         <v>6</v>
       </c>
       <c r="M115" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="N115" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O115"/>
     </row>
@@ -7142,28 +7142,28 @@
         <v>9</v>
       </c>
       <c r="G116" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H116" t="s">
         <v>10</v>
       </c>
       <c r="I116" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J116" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K116" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L116">
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="N116" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O116"/>
     </row>
@@ -7187,25 +7187,25 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H117" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I117" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J117" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K117" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L117">
         <v>6</v>
       </c>
       <c r="M117" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N117" t="s">
         <v>13</v>
@@ -7232,28 +7232,28 @@
         <v>9</v>
       </c>
       <c r="G118" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H118" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I118" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J118" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K118" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L118">
         <v>6</v>
       </c>
       <c r="M118" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N118" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O118"/>
     </row>
@@ -7277,34 +7277,34 @@
         <v>9</v>
       </c>
       <c r="G119" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H119" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I119" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J119" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K119" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L119">
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N119" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O119"/>
     </row>
     <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B120">
         <v>40707</v>
@@ -7313,7 +7313,7 @@
         <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E120" t="s">
         <v>19</v>
@@ -7322,25 +7322,25 @@
         <v>9</v>
       </c>
       <c r="G120" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H120" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I120" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J120" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K120" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L120">
         <v>6</v>
       </c>
       <c r="M120" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="N120" t="s">
         <v>13</v>
@@ -7349,7 +7349,7 @@
     </row>
     <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B121">
         <v>40708</v>
@@ -7358,7 +7358,7 @@
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
@@ -7367,34 +7367,34 @@
         <v>9</v>
       </c>
       <c r="G121" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H121" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I121" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J121" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K121" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L121">
         <v>6</v>
       </c>
       <c r="M121" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="N121" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O121"/>
     </row>
     <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B122">
         <v>40709</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E122" t="s">
         <v>19</v>
@@ -7412,34 +7412,34 @@
         <v>9</v>
       </c>
       <c r="G122" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H122" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I122" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J122" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K122" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="N122" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O122"/>
     </row>
     <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B123">
         <v>40710</v>
@@ -7448,7 +7448,7 @@
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -7457,25 +7457,25 @@
         <v>9</v>
       </c>
       <c r="G123" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H123" t="s">
         <v>10</v>
       </c>
       <c r="I123" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J123" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K123" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L123">
         <v>6</v>
       </c>
       <c r="M123" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N123" t="s">
         <v>13</v>
@@ -7484,7 +7484,7 @@
     </row>
     <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B124">
         <v>40711</v>
@@ -7493,7 +7493,7 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -7502,34 +7502,34 @@
         <v>9</v>
       </c>
       <c r="G124" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H124" t="s">
         <v>10</v>
       </c>
       <c r="I124" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J124" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K124" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L124">
         <v>6</v>
       </c>
       <c r="M124" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N124" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O124"/>
     </row>
     <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B125">
         <v>40712</v>
@@ -7538,7 +7538,7 @@
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -7547,34 +7547,34 @@
         <v>9</v>
       </c>
       <c r="G125" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H125" t="s">
         <v>10</v>
       </c>
       <c r="I125" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J125" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K125" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L125">
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N125" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O125"/>
     </row>
     <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B126">
         <v>40713</v>
@@ -7583,7 +7583,7 @@
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E126" t="s">
         <v>19</v>
@@ -7592,25 +7592,25 @@
         <v>9</v>
       </c>
       <c r="G126" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H126" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I126" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J126" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K126" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L126">
         <v>6</v>
       </c>
       <c r="M126" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N126" t="s">
         <v>13</v>
@@ -7619,7 +7619,7 @@
     </row>
     <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B127">
         <v>40714</v>
@@ -7628,7 +7628,7 @@
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E127" t="s">
         <v>19</v>
@@ -7637,34 +7637,34 @@
         <v>9</v>
       </c>
       <c r="G127" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H127" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I127" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J127" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K127" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L127">
         <v>6</v>
       </c>
       <c r="M127" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N127" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O127"/>
     </row>
     <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B128">
         <v>40715</v>
@@ -7673,7 +7673,7 @@
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E128" t="s">
         <v>19</v>
@@ -7682,34 +7682,34 @@
         <v>9</v>
       </c>
       <c r="G128" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H128" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I128" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J128" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K128" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L128">
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N128" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O128"/>
     </row>
     <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B129">
         <v>40716</v>
@@ -7718,7 +7718,7 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -7727,25 +7727,25 @@
         <v>9</v>
       </c>
       <c r="G129" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H129" t="s">
         <v>10</v>
       </c>
       <c r="I129" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J129" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K129" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L129">
         <v>6</v>
       </c>
       <c r="M129" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="N129" t="s">
         <v>13</v>
@@ -7754,7 +7754,7 @@
     </row>
     <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B130">
         <v>40717</v>
@@ -7763,7 +7763,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -7772,34 +7772,34 @@
         <v>9</v>
       </c>
       <c r="G130" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H130" t="s">
         <v>10</v>
       </c>
       <c r="I130" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J130" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K130" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L130">
         <v>6</v>
       </c>
       <c r="M130" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="N130" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O130"/>
     </row>
     <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B131">
         <v>40718</v>
@@ -7808,7 +7808,7 @@
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -7817,34 +7817,34 @@
         <v>9</v>
       </c>
       <c r="G131" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H131" t="s">
         <v>10</v>
       </c>
       <c r="I131" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J131" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K131" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="N131" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O131"/>
     </row>
     <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B132">
         <v>40719</v>
@@ -7853,7 +7853,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -7862,34 +7862,34 @@
         <v>9</v>
       </c>
       <c r="G132" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H132" t="s">
         <v>10</v>
       </c>
       <c r="I132" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J132" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K132" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L132">
         <v>6</v>
       </c>
       <c r="M132" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="N132" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="O132"/>
     </row>
     <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B133">
         <v>40720</v>
@@ -7898,7 +7898,7 @@
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -7907,28 +7907,28 @@
         <v>9</v>
       </c>
       <c r="G133" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H133" t="s">
         <v>10</v>
       </c>
       <c r="I133" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J133" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K133" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L133">
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="N133" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O133"/>
     </row>
@@ -7952,25 +7952,25 @@
         <v>9</v>
       </c>
       <c r="G134" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H134" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I134" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J134" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K134" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L134">
         <v>6</v>
       </c>
       <c r="M134" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="N134" t="s">
         <v>13</v>
@@ -7997,28 +7997,28 @@
         <v>9</v>
       </c>
       <c r="G135" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H135" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I135" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J135" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K135" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L135">
         <v>6</v>
       </c>
       <c r="M135" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="N135" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O135"/>
     </row>
@@ -8042,34 +8042,34 @@
         <v>9</v>
       </c>
       <c r="G136" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H136" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I136" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J136" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K136" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L136">
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="N136" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O136"/>
     </row>
     <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B137">
         <v>40728</v>
@@ -8078,7 +8078,7 @@
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E137" t="s">
         <v>19</v>
@@ -8087,25 +8087,25 @@
         <v>9</v>
       </c>
       <c r="G137" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H137" t="s">
         <v>20</v>
       </c>
       <c r="I137" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J137" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K137" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L137">
         <v>6</v>
       </c>
       <c r="M137" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="N137" t="s">
         <v>13</v>
@@ -8114,7 +8114,7 @@
     </row>
     <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B138">
         <v>40729</v>
@@ -8123,7 +8123,7 @@
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E138" t="s">
         <v>19</v>
@@ -8132,34 +8132,34 @@
         <v>9</v>
       </c>
       <c r="G138" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H138" t="s">
         <v>20</v>
       </c>
       <c r="I138" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J138" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K138" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L138">
         <v>6</v>
       </c>
       <c r="M138" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="N138" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O138"/>
     </row>
     <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B139">
         <v>40730</v>
@@ -8168,7 +8168,7 @@
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E139" t="s">
         <v>19</v>
@@ -8177,34 +8177,34 @@
         <v>9</v>
       </c>
       <c r="G139" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H139" t="s">
         <v>20</v>
       </c>
       <c r="I139" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J139" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K139" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="N139" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O139"/>
     </row>
     <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B140">
         <v>40731</v>
@@ -8213,7 +8213,7 @@
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E140" t="s">
         <v>19</v>
@@ -8222,25 +8222,25 @@
         <v>9</v>
       </c>
       <c r="G140" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H140" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I140" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J140" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K140" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L140">
         <v>6</v>
       </c>
       <c r="M140" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="N140" t="s">
         <v>13</v>
@@ -8249,7 +8249,7 @@
     </row>
     <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B141">
         <v>40732</v>
@@ -8258,7 +8258,7 @@
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E141" t="s">
         <v>19</v>
@@ -8267,34 +8267,34 @@
         <v>9</v>
       </c>
       <c r="G141" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H141" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I141" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J141" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K141" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L141">
         <v>6</v>
       </c>
       <c r="M141" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="N141" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O141"/>
     </row>
     <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B142">
         <v>40733</v>
@@ -8303,7 +8303,7 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E142" t="s">
         <v>19</v>
@@ -8312,34 +8312,34 @@
         <v>9</v>
       </c>
       <c r="G142" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H142" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I142" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J142" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K142" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L142">
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="N142" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O142"/>
     </row>
     <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B143">
         <v>40734</v>
@@ -8348,7 +8348,7 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E143" t="s">
         <v>19</v>
@@ -8357,25 +8357,25 @@
         <v>9</v>
       </c>
       <c r="G143" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H143" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I143" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J143" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K143" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L143">
         <v>6</v>
       </c>
       <c r="M143" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="N143" t="s">
         <v>13</v>
@@ -8384,7 +8384,7 @@
     </row>
     <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B144">
         <v>40735</v>
@@ -8393,7 +8393,7 @@
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E144" t="s">
         <v>19</v>
@@ -8402,34 +8402,34 @@
         <v>9</v>
       </c>
       <c r="G144" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H144" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I144" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J144" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K144" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L144">
         <v>6</v>
       </c>
       <c r="M144" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="N144" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O144"/>
     </row>
     <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B145">
         <v>40736</v>
@@ -8438,7 +8438,7 @@
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E145" t="s">
         <v>19</v>
@@ -8447,34 +8447,34 @@
         <v>9</v>
       </c>
       <c r="G145" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H145" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I145" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J145" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K145" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L145">
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="N145" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O145"/>
     </row>
     <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B146">
         <v>40737</v>
@@ -8483,7 +8483,7 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E146" t="s">
         <v>19</v>
@@ -8492,25 +8492,25 @@
         <v>9</v>
       </c>
       <c r="G146" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H146" t="s">
         <v>20</v>
       </c>
       <c r="I146" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J146" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K146" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L146">
         <v>6</v>
       </c>
       <c r="M146" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="N146" t="s">
         <v>13</v>
@@ -8519,7 +8519,7 @@
     </row>
     <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B147">
         <v>40738</v>
@@ -8528,7 +8528,7 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E147" t="s">
         <v>19</v>
@@ -8537,34 +8537,34 @@
         <v>9</v>
       </c>
       <c r="G147" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H147" t="s">
         <v>20</v>
       </c>
       <c r="I147" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J147" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K147" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L147">
         <v>6</v>
       </c>
       <c r="M147" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="N147" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O147"/>
     </row>
     <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B148">
         <v>40739</v>
@@ -8573,7 +8573,7 @@
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E148" t="s">
         <v>19</v>
@@ -8582,28 +8582,28 @@
         <v>9</v>
       </c>
       <c r="G148" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H148" t="s">
         <v>20</v>
       </c>
       <c r="I148" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J148" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K148" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L148">
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="N148" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O148"/>
     </row>
@@ -8627,25 +8627,25 @@
         <v>9</v>
       </c>
       <c r="G149" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H149" t="s">
         <v>28</v>
       </c>
       <c r="I149" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J149" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K149" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L149">
         <v>6</v>
       </c>
       <c r="M149" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="N149" t="s">
         <v>13</v>
@@ -8672,28 +8672,28 @@
         <v>9</v>
       </c>
       <c r="G150" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H150" t="s">
         <v>28</v>
       </c>
       <c r="I150" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J150" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K150" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L150">
         <v>6</v>
       </c>
       <c r="M150" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="N150" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="O150"/>
     </row>
@@ -8717,28 +8717,28 @@
         <v>9</v>
       </c>
       <c r="G151" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H151" t="s">
         <v>28</v>
       </c>
       <c r="I151" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J151" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K151" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L151">
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="N151" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O151"/>
     </row>
@@ -8762,25 +8762,25 @@
         <v>9</v>
       </c>
       <c r="G152" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H152" t="s">
         <v>28</v>
       </c>
       <c r="I152" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J152" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K152" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L152">
         <v>6</v>
       </c>
       <c r="M152" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="N152" t="s">
         <v>13</v>
@@ -8807,28 +8807,28 @@
         <v>9</v>
       </c>
       <c r="G153" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H153" t="s">
         <v>28</v>
       </c>
       <c r="I153" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J153" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K153" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L153">
         <v>6</v>
       </c>
       <c r="M153" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="N153" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="O153"/>
     </row>
@@ -8852,34 +8852,34 @@
         <v>9</v>
       </c>
       <c r="G154" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H154" t="s">
         <v>28</v>
       </c>
       <c r="I154" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J154" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K154" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L154">
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="N154" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O154"/>
     </row>
     <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B155">
         <v>40749</v>
@@ -8888,7 +8888,7 @@
         <v>26</v>
       </c>
       <c r="D155" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E155" t="s">
         <v>19</v>
@@ -8897,25 +8897,25 @@
         <v>9</v>
       </c>
       <c r="G155" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H155" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="I155" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J155" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K155" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L155">
         <v>6</v>
       </c>
       <c r="M155" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="N155" t="s">
         <v>13</v>
@@ -8924,7 +8924,7 @@
     </row>
     <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B156">
         <v>40750</v>
@@ -8933,7 +8933,7 @@
         <v>26</v>
       </c>
       <c r="D156" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E156" t="s">
         <v>19</v>
@@ -8942,34 +8942,34 @@
         <v>9</v>
       </c>
       <c r="G156" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H156" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="I156" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J156" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K156" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L156">
         <v>6</v>
       </c>
       <c r="M156" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="N156" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="O156"/>
     </row>
     <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B157">
         <v>40751</v>
@@ -8978,7 +8978,7 @@
         <v>26</v>
       </c>
       <c r="D157" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E157" t="s">
         <v>19</v>
@@ -8987,34 +8987,34 @@
         <v>9</v>
       </c>
       <c r="G157" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H157" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="I157" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J157" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K157" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L157">
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="N157" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O157"/>
     </row>
     <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B158">
         <v>40752</v>
@@ -9023,7 +9023,7 @@
         <v>26</v>
       </c>
       <c r="D158" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E158" t="s">
         <v>19</v>
@@ -9032,25 +9032,25 @@
         <v>9</v>
       </c>
       <c r="G158" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H158" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="I158" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J158" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K158" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L158">
         <v>6</v>
       </c>
       <c r="M158" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="N158" t="s">
         <v>13</v>
@@ -9059,7 +9059,7 @@
     </row>
     <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B159">
         <v>40753</v>
@@ -9068,7 +9068,7 @@
         <v>26</v>
       </c>
       <c r="D159" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E159" t="s">
         <v>19</v>
@@ -9077,34 +9077,34 @@
         <v>9</v>
       </c>
       <c r="G159" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H159" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="I159" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J159" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K159" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L159">
         <v>6</v>
       </c>
       <c r="M159" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="N159" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="O159"/>
     </row>
     <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B160">
         <v>40754</v>
@@ -9113,7 +9113,7 @@
         <v>26</v>
       </c>
       <c r="D160" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E160" t="s">
         <v>19</v>
@@ -9122,34 +9122,34 @@
         <v>9</v>
       </c>
       <c r="G160" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H160" t="s">
+        <v>185</v>
+      </c>
+      <c r="I160" t="s">
+        <v>76</v>
+      </c>
+      <c r="J160" t="s">
+        <v>77</v>
+      </c>
+      <c r="K160" t="s">
+        <v>65</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160" t="s">
         <v>193</v>
       </c>
-      <c r="I160" t="s">
-        <v>84</v>
-      </c>
-      <c r="J160" t="s">
-        <v>85</v>
-      </c>
-      <c r="K160" t="s">
-        <v>73</v>
-      </c>
-      <c r="L160">
-        <v>0</v>
-      </c>
-      <c r="M160" t="s">
-        <v>201</v>
-      </c>
       <c r="N160" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O160"/>
     </row>
     <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B161">
         <v>40755</v>
@@ -9158,7 +9158,7 @@
         <v>26</v>
       </c>
       <c r="D161" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E161" t="s">
         <v>19</v>
@@ -9167,25 +9167,25 @@
         <v>9</v>
       </c>
       <c r="G161" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H161" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="I161" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J161" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K161" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L161">
         <v>6</v>
       </c>
       <c r="M161" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="N161" t="s">
         <v>13</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B162">
         <v>40756</v>
@@ -9203,7 +9203,7 @@
         <v>26</v>
       </c>
       <c r="D162" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E162" t="s">
         <v>19</v>
@@ -9212,34 +9212,34 @@
         <v>9</v>
       </c>
       <c r="G162" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H162" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="I162" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J162" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K162" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L162">
         <v>6</v>
       </c>
       <c r="M162" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="N162" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="O162"/>
     </row>
     <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B163">
         <v>40757</v>
@@ -9248,7 +9248,7 @@
         <v>26</v>
       </c>
       <c r="D163" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E163" t="s">
         <v>19</v>
@@ -9257,28 +9257,28 @@
         <v>9</v>
       </c>
       <c r="G163" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H163" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="I163" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J163" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K163" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L163">
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="N163" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O163"/>
     </row>
@@ -9408,17 +9408,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -9619,6 +9608,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
   <ds:schemaRefs>
@@ -9628,17 +9628,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9655,4 +9644,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>